--- a/data/laborum/summary_data.xlsx
+++ b/data/laborum/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q358"/>
+  <dimension ref="A1:Q368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24128,6 +24128,664 @@
         </is>
       </c>
     </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Ayudante de Cocina</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Clínica del Carmen</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Macul, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/ayudante-de-cocina-1118371464.html</t>
+        </is>
+      </c>
+      <c r="G359" t="n">
+        <v>0</v>
+      </c>
+      <c r="H359" t="inlineStr"/>
+      <c r="I359" t="n">
+        <v>0</v>
+      </c>
+      <c r="J359" t="n">
+        <v>0</v>
+      </c>
+      <c r="K359" t="n">
+        <v>0</v>
+      </c>
+      <c r="L359" t="n">
+        <v>1</v>
+      </c>
+      <c r="M359" t="n">
+        <v>0</v>
+      </c>
+      <c r="N359" t="n">
+        <v>0</v>
+      </c>
+      <c r="O359" t="n">
+        <v>0</v>
+      </c>
+      <c r="P359" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>👨‍🍳 Resumen de Oferta Laboral: Ayudante de Cocina (Clínica)🎯 Propósito del Cargo Ejecutar procedimientos de alimentación usando técnicas culinarias y gastronómicas. Asegurar la calidad de atención al paciente y mantener una actitud respetuosa con todos los usuarios y trabajadores.📝 Funciones Principales Manipular y Elaborar alimentos según técnicas culinarias y gastronómicas, respetando las prescripciones dietéticas de la Nutricionista.  Aplicar estrictamente técnicas de higiene y sanitización (personal, ambiente, utensilios, equipos) según normas establecidas. Colaborar en los distintos puestos de la Unidad de Alimentación, apoyar en el porcionamiento y distribucion de alimentos.✅ Requisitos Clave Experiencia: Mínimo 2 años en servicios de alimentación y nutrición (Hospitales o Alimentación Colectiva). Certificación: Curso de Manipulador de Alimentos comprobable. Salud: Vacunas de Hepatitis B al día. Disponibilidad: Para Turnos 2X2, HORARIO DIURNO de 7:00 am a 19:00 pm.🗓️ Condiciones Laborales y BeneficiosTURNOS: 2x2Renta Líquida $553.553 LIQUIDO+ Horas Extras.Beneficios* 2 aguinaldos al año.* Sala Cuna.* 1 día libre por cumpleaños.* 6 dias administrativos al año</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Analista de remuneraciones</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Clínica Dávila Vespucio</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>La Florida, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/analista-de-remuneraciones-1118371883.html</t>
+        </is>
+      </c>
+      <c r="G360" t="n">
+        <v>2</v>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I360" t="n">
+        <v>0</v>
+      </c>
+      <c r="J360" t="n">
+        <v>0</v>
+      </c>
+      <c r="K360" t="n">
+        <v>0</v>
+      </c>
+      <c r="L360" t="n">
+        <v>1</v>
+      </c>
+      <c r="M360" t="n">
+        <v>0</v>
+      </c>
+      <c r="N360" t="n">
+        <v>0</v>
+      </c>
+      <c r="O360" t="n">
+        <v>0</v>
+      </c>
+      <c r="P360" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>Clínica Dávila Vespucio es el principal centro de salud privado de la zona sur oriente de Santiago y miembro del Grupo de Empresas Banmédica, buscamos favorecer e impulsar el valor de la inclusión, permitiendo crear equipos más humanos e integrales, acorde a la ley 20.422. Creemos en lugares de trabajo inclusivo, donde loas diferencias de las personas son respetadas, valoradas y atendidas para que todos nuestros colaboradores puedan desarrollar plenamente sus talentos. Se parte de Clinica Dávila Vespucio Es la persona responsable de conocer todas las áreas que componen el departamento de Recursos Humanos. Según tareas asignadas se hará responsables de la ejecución y el control de las áreas de Remuneraciones, Anexos, Finiquitos, Control de Asistencia, Contratos, Honorarios, Etc. Requisitos:  Título superior en administración de recursos humanos o carreras afines 2 años de experiencia en áreas relacionadas a remuneraciones Excel intermedio y conocimiento en legislación laboral  Beneficios  Casino institucional Seguros asociados</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Preparación de Muestras Minerales-Colina</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Colina, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/preparacion-de-muestras-minerales-colina-1118371459.html</t>
+        </is>
+      </c>
+      <c r="G361" t="n">
+        <v>1</v>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I361" t="n">
+        <v>0</v>
+      </c>
+      <c r="J361" t="n">
+        <v>0</v>
+      </c>
+      <c r="K361" t="n">
+        <v>0</v>
+      </c>
+      <c r="L361" t="n">
+        <v>1</v>
+      </c>
+      <c r="M361" t="n">
+        <v>0</v>
+      </c>
+      <c r="N361" t="n">
+        <v>0</v>
+      </c>
+      <c r="O361" t="n">
+        <v>0</v>
+      </c>
+      <c r="P361" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>Importante empresa del rubro laboratorio y servicios para la industria minera se encuentra en búsqueda de un/a Preparador/a de Muestras Minerales, responsable de ejecutar las actividades de recepción, preparación y acondicionamiento de muestras, asegurando el cumplimiento de los procedimientos operacionales, estándares de calidad y normativas de seguridad establecidas.Buscamos personas comprometidas, responsables y orientadas al trabajo en equipo, que deseen desarrollarse en procesos operacionales asociados a laboratorios y análisis de muestras minerales.Principales funciones Recepcionar e ingresar muestras al proceso productivo. Ejecutar actividades de secado, chancado y pulverizado de muestras minerales. Cumplir rigurosamente con los procedimientos operacionales y estándares de calidad establecidos. Realizar limpieza y mantenimiento básico de los equipos utilizados durante la operación. Mantener actualizados los registros operacionales y técnicos asociados al proceso. Reportar oportunamente cualquier incidente operativo o condición insegura a su supervisión directa. Apoyar en el cumplimiento de los programas de mantenimiento de equipos del área. Utilizar correctamente los elementos de protección personal y cumplir las normas de seguridad vigentes. Contribuir al cumplimiento de los objetivos operacionales y de calidad del laboratorio.Requisitos Enseñanza Media Completa (Técnico Profesional o Científico Humanista). Deseable experiencia mínima de 1 año en áreas productivas, industriales, mineras o de laboratorio. Conocimientos básicos en preparación de muestras o procesos operacionales. Capacidad para trabajar bajo procedimientos establecidos. Orientación al trabajo seguro. Capacidad de organización y trabajo en equipo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Empaquetadores Turnos Rotativos - NIU Express Mall Alto Las Condes</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Niu Foods</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Las Condes, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/empaquetadores-turnos-rotativos-niu-express-mall-alto-las-condes-1118372412.html</t>
+        </is>
+      </c>
+      <c r="G362" t="n">
+        <v>0</v>
+      </c>
+      <c r="H362" t="inlineStr"/>
+      <c r="I362" t="n">
+        <v>0</v>
+      </c>
+      <c r="J362" t="n">
+        <v>0</v>
+      </c>
+      <c r="K362" t="n">
+        <v>0</v>
+      </c>
+      <c r="L362" t="n">
+        <v>1</v>
+      </c>
+      <c r="M362" t="n">
+        <v>0</v>
+      </c>
+      <c r="N362" t="n">
+        <v>0</v>
+      </c>
+      <c r="O362" t="n">
+        <v>0</v>
+      </c>
+      <c r="P362" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>¡Seguimos creciendo y esta vez, con un formato renovado!Niu Sushi, la cadena de sushi con mas variedad de chile, llega con su nuevo formato NIU EXPRESS a MALL ALTO LAS CONDES para seguir deleitando a sus con sus clientes con frescos productos y su gran variedad en rolls. Niu Express Alto Las Condes se sumara a la gran familia Niu Foods, holding dedicado al rubro gastronomico que cuenta con mas de 60 locales a nivel nacional e internacional (Posicionandose con 3 locales en México).Por lo que estamos en la busqueda de Empaquetadores cuya principal función es recibir los productos desde cocina y barra e ir armando los pedidos rápidamente, verificando que vaya exactamente lo que solicito el cliente (pedido completo).Requisitos:- Experiencia en atención al cliente.- Disponibilida para trabajar en turnos rotativos (AM, intermedio, PM), entre lunes y domingo.- Documentación vigente (extranjeros con residencia definitiva).- Disponibilidad para trabajar en comuna de Las Condes.Horarios ROTATIVOS: SEMANA 5x2 Y 6x1- AM - INTERMEDIO - PM Renta base de $553.000 + Bono Asistencia $50.000 y además desde el segundo mes comenzarás a recibir bonos (por pedidos completos y pedidos a tiempo) con un valor que va desde los $50.000 hasta los $100.000 todo según tu desempeño + colación + uniforme y un grato ambiente de trabajo.Beneficios y Convenios: - Bono por referido (desde 25.000 a 50.000) - Desarrollo de carrera interna. - Bono al empleado del mes (50.000) - Convenios Oncologicos, dentales, Gimnasios. - Gif card de cumpleaños, Aguinaldos Septiembre y Diciembre (Al pasar a contrato Indefinido) - Escuela de formación a Susheros y Programas de formación de Líderes. - Seguro de Acccidentes ACHS. - Ingreso a caja de compensación Los Andes Y Descuentos del 20% en nuestros productos de la cadena.¡Adjunto tu CV y se parte de esta maravillosa experiencia y del gran equipo NIU!</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Full time , para Ventas digitales - 1.659.000</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Chillán, Región XVI</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Full-time - Remoto</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/full-time-para-ventas-digitales-1-659-000-1118372364.html</t>
+        </is>
+      </c>
+      <c r="G363" t="n">
+        <v>0</v>
+      </c>
+      <c r="H363" t="inlineStr"/>
+      <c r="I363" t="n">
+        <v>0</v>
+      </c>
+      <c r="J363" t="n">
+        <v>1</v>
+      </c>
+      <c r="K363" t="n">
+        <v>0</v>
+      </c>
+      <c r="L363" t="n">
+        <v>0</v>
+      </c>
+      <c r="M363" t="n">
+        <v>1</v>
+      </c>
+      <c r="N363" t="n">
+        <v>0</v>
+      </c>
+      <c r="O363" t="n">
+        <v>0</v>
+      </c>
+      <c r="P363" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>Buscamos personas de cualquier edad para trabajar en Ventas digitales Full time / $1.659.000 mensuales aproximadosTRABAJO DE VENTAS con modalidad REMOTO (horarios flexibles)Las ventas se realizan a traves de Pagina web y contamos con envios gratuitos a todo el pais .Recibiras:Sitio web personal. (Gratis)App Movil (opcional)Call center gratuito para ti y tus clientesEntrenamientos virtuales semanales constantesBono el primer día y ademas mensuales en dinero*Tambien tenemos formato PART-TIME especial para estudiantes o personas que necesitan un segundo ingreso o trabajar desde su casa.Postula ahora y accede a la informacion detallada y reunión virtual</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Valdivia: Ejecutivo-a Comercial En Terreno | Renta Base + Incentivo</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Atento Chile S.A</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Valdivia, Región XIV</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/valdivia-ejecutivo-a-comercial-en-terreno-renta-base-incentivo-1118371879.html</t>
+        </is>
+      </c>
+      <c r="G364" t="n">
+        <v>0</v>
+      </c>
+      <c r="H364" t="inlineStr"/>
+      <c r="I364" t="n">
+        <v>0</v>
+      </c>
+      <c r="J364" t="n">
+        <v>0</v>
+      </c>
+      <c r="K364" t="n">
+        <v>0</v>
+      </c>
+      <c r="L364" t="n">
+        <v>1</v>
+      </c>
+      <c r="M364" t="n">
+        <v>0</v>
+      </c>
+      <c r="N364" t="n">
+        <v>0</v>
+      </c>
+      <c r="O364" t="n">
+        <v>0</v>
+      </c>
+      <c r="P364" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>Valdivia: Ejecutivo/a Comercial En Terreno | Renta Base + IncentivoNos encontramos en búsqueda de personas con orientación comercial y experiencia en ventas para incorporarse a un importante equipo dedicado a la comercialización de servicios de Fibra Óptica y RGU en la ciudad de Antofagasta.El objetivo del cargo es generar nuevas oportunidades de negocio, captar clientes y contribuir al crecimiento comercial mediante una gestión principalmente en terreno.📡Principales responsabilidades Prospectar clientes en proyectos inmobiliarios. Desarrollar actividades comerciales en distintos sectores de Antofagasta. Identificar oportunidades de negocio y concretar ventas. Utilizar herramientas digitales para el registro y seguimiento de la gestión comercial. Cumplir metas e indicadores asociados al cargo.📡Oferta económica: Sueldo base: $539.000 Asignación de movilización: $51.219 Asignación de colación: $51.219 Bono de ingreso primer mes: $100.000 bruto Incentivo variable: $483.000 Bono por sobrecumplimiento de hasta $160.000 Semana corrida estimada: $109.773Todos los montos señalados son imponibles.📡Beneficios y condiciones Contratación desde el primer día de capacitación. Herramientas digitales para apoyar la gestión comercial. Oportunidad de desarrollar una carrera en un entorno orientado al cumplimiento de objetivos y resultados.📡Modalidad de trabajo Modalidad: 90% terreno y 10% oficina. Jornada de 42 horas semanales. Lunes a viernes: turnos rotativos entre las 09:00 y las 20:00 horas. Sábados: de 10:00 a 14:00 horas.📡Requisitos de postulación: Enseñanza Media Completa. Al menos 6 meses de experiencia en ventas. Disponibilidad para desempeñarse principalmente en terreno. Motivación por los desafíos comerciales. Orientación al cumplimiento de metas y resultados.👉Esta oferta laboral se encuentra abierta a personas en situación de discapacidad en el marco de la Ley N.° 21.015.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Ejecutivo-a de Ventas de Seguros - Concepción</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>PeopleGo</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Concepción, Región VIII</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/ejecutivo-a-de-ventas-de-seguros-concepcion-1118358904.html</t>
+        </is>
+      </c>
+      <c r="G365" t="n">
+        <v>0</v>
+      </c>
+      <c r="H365" t="inlineStr"/>
+      <c r="I365" t="n">
+        <v>0</v>
+      </c>
+      <c r="J365" t="n">
+        <v>0</v>
+      </c>
+      <c r="K365" t="n">
+        <v>0</v>
+      </c>
+      <c r="L365" t="n">
+        <v>1</v>
+      </c>
+      <c r="M365" t="n">
+        <v>0</v>
+      </c>
+      <c r="N365" t="n">
+        <v>0</v>
+      </c>
+      <c r="O365" t="n">
+        <v>0</v>
+      </c>
+      <c r="P365" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>People Go es una empresa al servicio de las personas, siempre comprometida con la diversidad e inclusión en sus infinitas formas, personalidades, culturas, etnias, origen, identidad, religión, edad, gustos y capacidades.En People Go actualmente buscamos Ejecutivos/as de Venta para unos de nuestros importantes clientes. Si eres una persona apasionada por el área y te interesa trabajar en un ambiente dinámico y profesional, te invitamos a postular.¿Qué harás en este rol? Promocionar, asesorar y comercializar seguros complementarios de salud, brindando soluciones personalizadas a clientes individuales. El objetivo principal es captar nuevos asegurados y fidelizar la cartera existente, cumpliendo metas mensuales de ventas y satisfacción del cliente. Asesorar a clientes sobre los beneficios, coberturas y condiciones de los seguros complementarios de salud. Mantener una gestión activa de seguimiento y cierre de ventas.Requisitos: Contar con al menos 1 año de experiencia en ventas de productos intangibles (excluyente). Deseable experiencia en seguros de ISAPRES, AFP o Telefonía. Disponibilidad para trabajar por sistema de turnos.Condiciones laborales: Contrato directo con Vida Cámara. Modalidad: presencial en sucursal asignada según residencia. Jornada de 40 horas semanales por sistema de turnos A.M y PM, 2 sábados al mes. Renta líquida de $680.000 + comisiones sin tope.¡Si cumples con los requisitos y te entusiasma participar en el proceso de selección no dudes en postular, te esperamos!</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>ADMINISTRADOR RUBRO GASTRONOMICO - CONCEPCIÓN</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Niu Foods</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Concepción, Región VIII</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/administrador-rubro-gastronomico-concepcion-1118277703.html</t>
+        </is>
+      </c>
+      <c r="G366" t="n">
+        <v>0</v>
+      </c>
+      <c r="H366" t="inlineStr"/>
+      <c r="I366" t="n">
+        <v>0</v>
+      </c>
+      <c r="J366" t="n">
+        <v>0</v>
+      </c>
+      <c r="K366" t="n">
+        <v>0</v>
+      </c>
+      <c r="L366" t="n">
+        <v>1</v>
+      </c>
+      <c r="M366" t="n">
+        <v>0</v>
+      </c>
+      <c r="N366" t="n">
+        <v>0</v>
+      </c>
+      <c r="O366" t="n">
+        <v>0</v>
+      </c>
+      <c r="P366" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>!!SE PARTE DE NUESTRO EQUIPO DEL NIU SUSHI CONCEPCIÓN!!Importante Holding del Rubro Gastronómico está en búsqueda de Sub Gerente para unirse a su prestigiosa cadena que cuenta actualmente con 60 locales.Ofrecemos capacitación y pasantías internas (las cuales son obligatorias independiente de los conocimientos y experiencia con que vengan), para posicionarse con todas las herramientas necesarias para Liderar nuestros equipos de trabajo.Se trabaja: Jornada laboral en formato de locales de lunes a sábado o en formato de locales en Mall de lunes a domingo, en Horario PM de 17:30hrs hasta el cierre de local. Se trabaja con ARTÍCULO 22.Lugar: ConcepciónOfrecemos estabilidad Laboral, Trabajo en Equipo, Oportunidad de perfeccionamiento y crecimiento interno, Un grato ambiente de trabajo y permanecer a una cadena líder en el mercado del Sushi.Sueldo Base por período de capacitación $600.000 + $200.000 de bono por periodo de capacitación + Bonos por cumplimiento de Metas una vez finalizado el proceso de capacitación.CUALIFICACIONES- Es necesario poseer un título técnico o profesional en áreas a fines.- Idealmente con 1 o 2 años de experiencia previa en el rubro gastronómico.- Disponibilidad de trabajo en el turno PM.BENEFICIOS- Posibilidad de crecimiento y desarrollo interno.- Convenios con gimnasio- Convenios Psicólogicos- Convenios con Clinicas Odontologícas- Seguro de Accidentes ACHSTE ESPERAMOS!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>SUBGERENTE DE LOCAL RUBRO GASTRONOMICO - CONCEPCIÓN</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Niu Foods</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Concepción, Región VIII</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/subgerente-de-local-rubro-gastronomico-concepcion-1118078257.html</t>
+        </is>
+      </c>
+      <c r="G367" t="n">
+        <v>0</v>
+      </c>
+      <c r="H367" t="inlineStr"/>
+      <c r="I367" t="n">
+        <v>0</v>
+      </c>
+      <c r="J367" t="n">
+        <v>0</v>
+      </c>
+      <c r="K367" t="n">
+        <v>0</v>
+      </c>
+      <c r="L367" t="n">
+        <v>1</v>
+      </c>
+      <c r="M367" t="n">
+        <v>0</v>
+      </c>
+      <c r="N367" t="n">
+        <v>0</v>
+      </c>
+      <c r="O367" t="n">
+        <v>0</v>
+      </c>
+      <c r="P367" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>!!SE PARTE DE NUESTRO EQUIPO DEL NIU SUSHI CONCEPCIÓN!!Importante Holding del Rubro Gastronómico está en búsqueda de Sub Gerente para unirse a su prestigiosa cadena que cuenta actualmente con 60 locales.Ofrecemos capacitación y pasantías internas (las cuales son obligatorias independiente de los conocimientos y experiencia con que vengan), para posicionarse con todas las herramientas necesarias para Liderar nuestros equipos de trabajo.Se trabaja: Jornada laboral en formato de locales de lunes a sábado o en formato de locales en Mall de lunes a domingo, en Horario PM de 17:30hrs hasta el cierre de local. Se trabaja con ARTÍCULO 22.Lugar: ConcepciónOfrecemos estabilidad Laboral, Trabajo en Equipo, Oportunidad de perfeccionamiento y crecimiento interno, Un grato ambiente de trabajo y permanecer a una cadena líder en el mercado del Sushi.Sueldo Base por período de capacitación $600.000 + $200.000 de bono por periodo de capacitación + Bonos por cumplimiento de Metas una vez finalizado el proceso de capacitación.CUALIFICACIONES- Es necesario poseer un título técnico o profesional en áreas a fines.- Idealmente con 1 o 2 años de experiencia previa en el rubro gastronómico.- Disponibilidad de trabajo en el turno PM.BENEFICIOS- Posibilidad de crecimiento y desarrollo interno.- Convenios con gimnasio- Convenios Psicólogicos- Convenios con Clinicas Odontologícas- Seguro de Accidentes ACHSTE ESPERAMOS!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Ayudante de Cocina Turnos Rotativos - NIU Express Mall Alto Las Condes</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Niu Foods</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Las Condes, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/ayudante-de-cocina-turnos-rotativos-niu-express-mall-alto-las-condes-1117946441.html</t>
+        </is>
+      </c>
+      <c r="G368" t="n">
+        <v>0</v>
+      </c>
+      <c r="H368" t="inlineStr"/>
+      <c r="I368" t="n">
+        <v>0</v>
+      </c>
+      <c r="J368" t="n">
+        <v>0</v>
+      </c>
+      <c r="K368" t="n">
+        <v>0</v>
+      </c>
+      <c r="L368" t="n">
+        <v>1</v>
+      </c>
+      <c r="M368" t="n">
+        <v>0</v>
+      </c>
+      <c r="N368" t="n">
+        <v>0</v>
+      </c>
+      <c r="O368" t="n">
+        <v>0</v>
+      </c>
+      <c r="P368" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>¡Seguimos creciendo y esta vez, con un formato renovado!Niu Sushi, la cadena de sushi con mas variedad de chile, llega con su nuevo formato NIU EXPRESS a MALL PARQUE ARAUCO para seguir deleitando a sus con sus clientes con frescos productos y su gran variedad en rolls. Niu Express ALTO LAS CONDES se sumara a la gran familia Niu Foods, holding dedicado al rubro gastronomico que cuenta con mas de 60 locales a nivel nacional e internacional (Posicionandose con 3 locales en México).Por lo que estamos en la busqueda de Ayudantes de Cocina con experiencia para formar parte de nuestro nuevo equipo.Requisitos:- Mínimo 1 año de experiencia en labores en cuarto frío y cuarto caliente.- Disponibilida para trabajar en turnos rotativos (AM, intermedio, PM), entre lunes y domingo.- Documentación vigente (extranjeros con residencia definitiva).- Disponibilidad para trabajar en comuna de Las Condes.- Disponibilidad para entrenarse en otro de nuestros locales activos de la cadena, hasta la apertura de su local de destino. (Entrenamiento pagado)Horarios ROTATIVOS: SEMANA 5x2 Y 6x1- FULL TIME (AM -INTERMEDIO - PM)Sueldo Base: $553.000 + Bono Asistencia $50.000 + Bono producción (variable) + colación + uniforme.Beneficios y Convenios: - Bono por referido (desde 25.000 a 50.000) - Desarrollo de carrera interna. - Bono al empleado del mes (50.000) - Convenios Oncologicos, dentales, Gimnasios. - Gif card de cumpleaños, Aguinaldos Septiembre y Diciembre (Al pasar a contrato Indefinido) - Escuela de formación a Susheros y Programas de formación de Líderes. - Seguro de Acccidentes ACHS. - Ingreso a caja de compensación Los Andes Y Descuentos del 20% en nuestros productos de la cadena.¡Adjunto tu CV y se parte de esta maravillosa experiencia y del gran equipo NIU!</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/laborum/summary_data.xlsx
+++ b/data/laborum/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q368"/>
+  <dimension ref="A1:Q393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24786,6 +24786,1651 @@
         </is>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Jefa de Tienda - Local Comercial Mallplaza Premium Outlets Concepción - Ex Mirador Bio Bio</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Concepción, Región VIII</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/jefa-de-tienda-local-comercial-mallplaza-premium-outlets-concepcion-ex-mirador-bio-bio-1118372710.html</t>
+        </is>
+      </c>
+      <c r="G369" t="n">
+        <v>0</v>
+      </c>
+      <c r="H369" t="inlineStr"/>
+      <c r="I369" t="n">
+        <v>0</v>
+      </c>
+      <c r="J369" t="n">
+        <v>0</v>
+      </c>
+      <c r="K369" t="n">
+        <v>0</v>
+      </c>
+      <c r="L369" t="n">
+        <v>1</v>
+      </c>
+      <c r="M369" t="n">
+        <v>0</v>
+      </c>
+      <c r="N369" t="n">
+        <v>0</v>
+      </c>
+      <c r="O369" t="n">
+        <v>0</v>
+      </c>
+      <c r="P369" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>Empresa de vestuario femenino, con mas de 100 años, con presencia a nivel nacional en todas las regiones y mas de 30 tiendas, te invita a formar parte de su equipo de trabajo como Jefa de Tienda, para nuestro nuevo Local Comercial Mallplaza Premium Outlets Concepción - Ex Mirador Bio Bio, ¡el que abriremos proximamente!.Dentro de las funciones principales esta la administración comercial, de ventas, y de recursos humanos del local, implementando estrategias comerciales y de control de gestión, para asegurar el logro de las metas y constante mejoramiento.La búsqueda está dirigida a personas con solidas capacidades de liderazgo y direccion de equipos, orientación al cliente, motivación, proactividad y gestion comercial.Te ofrecemos incorporarte a una gran empresa, con 30 tiendas a lo largo del pais, con grato ambiente laboral, beneficios y reconocimientos, oportunidades de desarrollo personal y profesional. Si eres una persona dinámica, positiva, íntegra, tienes buenas habilidades comunicacionales y orientación al servicio al cliente, únete a nuestro equipo.Te invitamos a postular y participar de nuestro proceso de reclutamiento y selección y ser parte de esta gran empresa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Jefe de Seguridad</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Santiago de Chile, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/jefe-de-seguridad-1118372700.html</t>
+        </is>
+      </c>
+      <c r="G370" t="n">
+        <v>0</v>
+      </c>
+      <c r="H370" t="inlineStr"/>
+      <c r="I370" t="n">
+        <v>0</v>
+      </c>
+      <c r="J370" t="n">
+        <v>0</v>
+      </c>
+      <c r="K370" t="n">
+        <v>0</v>
+      </c>
+      <c r="L370" t="n">
+        <v>1</v>
+      </c>
+      <c r="M370" t="n">
+        <v>0</v>
+      </c>
+      <c r="N370" t="n">
+        <v>0</v>
+      </c>
+      <c r="O370" t="n">
+        <v>0</v>
+      </c>
+      <c r="P370" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>Empresa manufacturera con casa matriz en Huechuraba, se encuentra en búsqueda de un Jefe de Seguridad para liderar la gestión de seguridad física y patrimonial de sus instalaciones en la RM.Misión del cargo: Garantizar la seguridad física y patrimonial de las instalaciones, personas y activos de la empresa, mediante la planificación, supervisión y ejecución de los protocolos de seguridad, control de accesos y gestión de contingencias, liderando al equipo de guardias y supervisores con un enfoque disciplinado, preventivo y orientado al cumplimiento normativo.Funciones principales Liderar, coordinar y evaluar al equipo de guardias OS10 y supervisores de turno. Controlar el acceso de personas, vehículos y mercadería a las instalaciones. Administrar los sistemas de CCTV, alarmas y control de accesos. Elaborar y actualizar protocolos de emergencia, evacuación y respuesta ante incidentes. Investigar y reportar incidentes de seguridad o pérdidas patrimoniales. Coordinar con Carabineros, PDI, bomberos y otras entidades externas ante emergencias. Gestionar la relación con empresas externas de seguridad y vigilancia. Capacitar al personal de seguridad en procedimientos y atención de contingencias.Requisitos Ex oficial o suboficial de Fuerzas Armadas (Ejército, Armada o FACh) o Carabineros/PDI. Deseable curso OS10 vigente o cursable. Mínimo 5 años de experiencia general en seguridad, con al menos 3 años en jefatura o mando de personal. Conocimientos en seguridad patrimonial e industrial, protocolos de emergencia, CCTV y control de accesos. Disponibilidad para trasladarse a distintas plantas en la RM.  Disponibilidad para atender contingencias fuera de horario habitual.Ofrecemos Renta acorde al mercado y a la experiencia del/la candidato/a. Estabilidad laboral y desarrollo profesional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Emprende en RE-MAX como Agente Inmobiliario con tus propios Horarios: Te capacitamos Y Acompañamos</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>REMAX-CENTRAL</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Las Condes, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Por Horas - Híbrido</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/emprende-en-re-max-como-agente-inmobiliario-con-tus-propios-horarios-te-capacitamos-y-acompanamos-1118372601.html</t>
+        </is>
+      </c>
+      <c r="G371" t="n">
+        <v>3</v>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>modelo</t>
+        </is>
+      </c>
+      <c r="I371" t="n">
+        <v>0</v>
+      </c>
+      <c r="J371" t="n">
+        <v>0</v>
+      </c>
+      <c r="K371" t="n">
+        <v>1</v>
+      </c>
+      <c r="L371" t="n">
+        <v>0</v>
+      </c>
+      <c r="M371" t="n">
+        <v>0</v>
+      </c>
+      <c r="N371" t="n">
+        <v>0</v>
+      </c>
+      <c r="O371" t="n">
+        <v>0</v>
+      </c>
+      <c r="P371" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>No es necesario tener experiencia, nosotros te Capacitamos!!!Si estás buscando un cambio en tu vida, valoras la libertad y obtener altos ingresos en una industria con alta demanda y contar con el apoyo de la MARCA inmobiliaria Nº1 del mundo, entonces en RE/MAX tenemos un lugar para ti.¿Qué ofrecemos?:Marca: RE/MAX es la marca de bienes raíces que más vende en el mundo.Independencia: En RE/MAX no hay horario, eres dueño de tu tiempo y de tus ingresos.Emprendimiento: Te ofrecemos la posibilidad de desarrollar tu propio negocio en el ámbito inmobiliario según tus propios objetivos.Metas: Las metas comerciales las determinas tú, según tus propias necesidades y expectativas. Nosotros te ayudamos a cumplirlas. Tenemos las comisiones más altas del mercado (36%-73%), no hay ingreso fijo.Capacitación: Nuestra oferta de formación y capacitación es la más completa del Mercado Inmobiliario: Bienvenido a RE/MAX (curso de inducción), Despega (Curso especializado de prospección de clientes) Follow UP (Mentorías personalizadas de seguimiento) RE/MAX University (Cursos online con actualización constante) Academia RE/MAX CENTRAL (talleres y rol play para aprender haciendo).Networking: Trabaja de manera colaborativa y aprende junto a una amplia red de agentes a nivel nacional e internacional, a través de un portal digital corporativo.Áreas de Apoyo: Contamos con un equipo multidisciplinario de profesionales que te ayudarán a obtener el éxito de tu negocio: Área Legal /Área Comercial- Tasación/Área de Comunicación- Marketing.Oficina Virtual: Trabaja desde donde quieras, contamos con recursos online para apoyarte y capacitarte de manera online.Oficina Física: Si quiere puedes trabajar desde nuestra oficina, ubicada a pasos del Metro Manquehue en Las Condes, encontrarás espacios de trabajo y salas para capacitación, reuniones y atención de clientes.Tecnología: Accede a los portales de publicación de propiedades más importante del mercado sin costo, al igual que a software de gestión inmobiliaria especializados y Marketing Digital, desarrollados exclusivamente por RE/MAX.Top Producer: Aprende de la experiencia de los Agentes Top Producer de nuestra oficina, quienes te compartirán sus estrategias para ser los número uno en venta a nivel nacional.Requisitos:-Excelente manejo de relaciones interpersonales.-Alta capacidad de autogestión, planificación, organización y motivación.-Ganas de ser independiente, tus ingresos dependen solo de tu propia gestión. No hay sueldo fijo.¿Quieres conocer más de nuestro modelo?Postula a este aviso y agendaremos una reunión online para contarte de la propuesta.Súmate a la RED de Agentes Inmobiliarios más grande del mercado y desarrolla junto a nosotros tu carrera como Emprendedor Inmobiliario.¡Te esperamos!</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Auxiliar de Farmacia - Colina</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Farmacias Ahumada SPA</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Colina, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/auxiliar-de-farmacia-colina-1118372737.html</t>
+        </is>
+      </c>
+      <c r="G372" t="n">
+        <v>0</v>
+      </c>
+      <c r="H372" t="inlineStr"/>
+      <c r="I372" t="n">
+        <v>0</v>
+      </c>
+      <c r="J372" t="n">
+        <v>0</v>
+      </c>
+      <c r="K372" t="n">
+        <v>0</v>
+      </c>
+      <c r="L372" t="n">
+        <v>1</v>
+      </c>
+      <c r="M372" t="n">
+        <v>0</v>
+      </c>
+      <c r="N372" t="n">
+        <v>0</v>
+      </c>
+      <c r="O372" t="n">
+        <v>0</v>
+      </c>
+      <c r="P372" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>Desde nuestra primera apertura en 1969 en la emblemática calle Ahumada de Santiago Centro, hemos crecido y evolucionado para convertirnos en la cadenafarmacéutica chilena con mayor trayectoria del país. Con más de 55 años de historia, Farmacias Ahumada es un referente en el cuidado de la salud en Chile.Nuestro compromiso con la comunidad y la excelencia en el servicio se refleja en nuestras más de 300 farmacias a lo largo del país, respaldadas por más de 2.800 colaboradores, un moderno Centro de Distribución, Oficinas Corporativas y un Recetario Magistral con altos estándares de calidad.Nuestro propósito es claro: ser líderes en el cuidado de las personas. Nos destacamos como expertos en salud, proporcionando una atención integral ypersonalizada a nuestros pacientes para mejorar su calidad de vida y la de sus familias.En esta fase de crecimiento, nos enfocamos en implementar diversas mejoras, enfrentando los nuevos desafíos con foco en nuestros colaboradores y clientes.Fortalecemos nuestro programa de fidelización para brindar soluciones y servicios a más personas, apostando por ofrecer una experiencia consistente en todos los puntos de contacto, desde un e-commerce llamativo y amigable hasta farmacias atractivas y competitivas.Las farmacias y sus colaboradores son el corazón de nuestro negocio. Nos distinguimos por un enfoque centrado en el paciente y un firme compromiso con lasalud y el bienestar de la comunidad. Nuestra amplia trayectoria y constante búsqueda de la excelencia nos consolidan como la opción experta y líder en el sector farmacéutico chileno.Promovemos una cultura centrada en la conciliación de la vida personal, familiar y laboral. A través de programas de capacitación, políticas de contratacióninclusivas y oportunidades de desarrollo profesional, buscamos garantizar que todos los miembros de nuestro equipo tengan las herramientas y el apoyo necesarios para alcanzar su máximo potencial.¡Somos Ahumada, tu aliado en salud y bienestar! Si eres Auxiliar de Farmacia y te caracterizas por tu vocación de servicio y experiencia, ayúdanos a brindar a nuestros pacientes la asesoría y el cuidado que necesitan, entregando un mayor acceso a la salud.¿Qué tendrás que hacer?-Realizar el proceso de atención y venta al paciente-cliente.- Derivar todas las consultas farmacológicas al Químico Farmacéutico de turno, como también las solicitudes de devolución o cambios de productos.- Revisar y reponer diariamente productos en las estanterías.- Llevar el control diario de las fechas de vencimiento de los productos.- Participar activamente de todos los inventarios. Requisitos: Para ser parte de nuestro equipo debes contar con:- Certificado o carnet de Auxiliar de Farmacia otorgado por la SEREMI o Título de Técnico en Farmacia.- Contar con Enseñanza media completa- Tener disponibilidad para trabajar de lunes a domingos en turnos rotativos de 6x1, con un día libre a la semana más 2 domingos libres al mes.¡Te esperamos!</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Auxiliar de Farmacia - La Reina 20horas</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Farmacias Ahumada SPA</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>La Reina, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Part-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/auxiliar-de-farmacia-la-reina-20horas-1118372734.html</t>
+        </is>
+      </c>
+      <c r="G373" t="n">
+        <v>0</v>
+      </c>
+      <c r="H373" t="inlineStr"/>
+      <c r="I373" t="n">
+        <v>0</v>
+      </c>
+      <c r="J373" t="n">
+        <v>0</v>
+      </c>
+      <c r="K373" t="n">
+        <v>0</v>
+      </c>
+      <c r="L373" t="n">
+        <v>1</v>
+      </c>
+      <c r="M373" t="n">
+        <v>1</v>
+      </c>
+      <c r="N373" t="n">
+        <v>0</v>
+      </c>
+      <c r="O373" t="n">
+        <v>0</v>
+      </c>
+      <c r="P373" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>Desde nuestra primera apertura en 1969 en la emblemática calle Ahumada de Santiago Centro, hemos crecido y evolucionado para convertirnos en la cadenafarmacéutica chilena con mayor trayectoria del país. Con más de 55 años de historia, Farmacias Ahumada es un referente en el cuidado de la salud en Chile.Nuestro compromiso con la comunidad y la excelencia en el servicio se refleja en nuestras más de 300 farmacias a lo largo del país, respaldadas por más de 2.800 colaboradores, un moderno Centro de Distribución, Oficinas Corporativas y un Recetario Magistral con altos estándares de calidad.Nuestro propósito es claro: ser líderes en el cuidado de las personas. Nos destacamos como expertos en salud, proporcionando una atención integral ypersonalizada a nuestros pacientes para mejorar su calidad de vida y la de sus familias.En esta fase de crecimiento, nos enfocamos en implementar diversas mejoras, enfrentando los nuevos desafíos con foco en nuestros colaboradores y clientes.Fortalecemos nuestro programa de fidelización para brindar soluciones y servicios a más personas, apostando por ofrecer una experiencia consistente en todos los puntos de contacto, desde un e-commerce llamativo y amigable hasta farmacias atractivas y competitivas.Las farmacias y sus colaboradores son el corazón de nuestro negocio. Nos distinguimos por un enfoque centrado en el paciente y un firme compromiso con lasalud y el bienestar de la comunidad. Nuestra amplia trayectoria y constante búsqueda de la excelencia nos consolidan como la opción experta y líder en el sector farmacéutico chileno.Promovemos una cultura centrada en la conciliación de la vida personal, familiar y laboral. A través de programas de capacitación, políticas de contratacióninclusivas y oportunidades de desarrollo profesional, buscamos garantizar que todos los miembros de nuestro equipo tengan las herramientas y el apoyo necesarios para alcanzar su máximo potencial.¡Somos Ahumada, tu aliado en salud y bienestar! Farmacia Ahumada, se encuentra en búsqueda de Auxiliares de Farmacia para unirse a nuestros equipos. Si tienes pasión por el cuidado de la salud, la atención al paciente y quieres formar parte de una empresa con más de 55 años de experiencia en el mercado farmacéutico, ¡esta oportunidad es para ti!Como Auxiliar de Farmacia, reconocido por la SEREMI de Salud, tendrás la importante misión de brindar una atención integral y personalizada a nuestros pacientes, contribuyendo a mejorar su calidad de vida y la de sus familias. Tus funciones principales incluirán asistir en la dispensación de medicamentos, atención al público, gestión de inventario y colaborar en la organización y limpieza de la farmacia.Buscamos personas comprometidas, proactivas y con vocación de servicio, que cuenten con un nivel educativo secundario graduado. La modalidad de trabajo es presencial y en un horario part time 20 horas semanales, distribuidos sábados, domingos y festivos.Te invitamos a participar de las vacantes, excelente nivel de ventas, grato ambiente laboral, ¡locales acondicionados para un mejor desempaño!  Requisitos: -Certificado o carnet de Auxiliar de Farmacia otorgado por la SEREMI o Título de Técnico en Farmacia,.-Contar con Enseñanza media completa-Tener disponibilidad para trabajar 20 horas, las cuales se distribuyen entre Sabados, Domingos y Festivos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Apoyo Logístico - Colina</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Farmacias Ahumada SPA</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Colina, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/apoyo-logistico-colina-1118372732.html</t>
+        </is>
+      </c>
+      <c r="G374" t="n">
+        <v>0</v>
+      </c>
+      <c r="H374" t="inlineStr"/>
+      <c r="I374" t="n">
+        <v>0</v>
+      </c>
+      <c r="J374" t="n">
+        <v>0</v>
+      </c>
+      <c r="K374" t="n">
+        <v>0</v>
+      </c>
+      <c r="L374" t="n">
+        <v>1</v>
+      </c>
+      <c r="M374" t="n">
+        <v>0</v>
+      </c>
+      <c r="N374" t="n">
+        <v>0</v>
+      </c>
+      <c r="O374" t="n">
+        <v>0</v>
+      </c>
+      <c r="P374" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>Desde nuestra primera apertura en 1969 en la emblemática calle Ahumada de Santiago Centro, hemos crecido y evolucionado para convertirnos en la cadenafarmacéutica chilena con mayor trayectoria del país. Con más de 55 años de historia, Farmacias Ahumada es un referente en el cuidado de la salud en Chile.Nuestro compromiso con la comunidad y la excelencia en el servicio se refleja en nuestras más de 300 farmacias a lo largo del país, respaldadas por más de 2.800 colaboradores, un moderno Centro de Distribución, Oficinas Corporativas y un Recetario Magistral con altos estándares de calidad.Nuestro propósito es claro: ser líderes en el cuidado de las personas. Nos destacamos como expertos en salud, proporcionando una atención integral ypersonalizada a nuestros pacientes para mejorar su calidad de vida y la de sus familias.En esta fase de crecimiento, nos enfocamos en implementar diversas mejoras, enfrentando los nuevos desafíos con foco en nuestros colaboradores y clientes.Fortalecemos nuestro programa de fidelización para brindar soluciones y servicios a más personas, apostando por ofrecer una experiencia consistente en todos los puntos de contacto, desde un e-commerce llamativo y amigable hasta farmacias atractivas y competitivas.Las farmacias y sus colaboradores son el corazón de nuestro negocio. Nos distinguimos por un enfoque centrado en el paciente y un firme compromiso con lasalud y el bienestar de la comunidad. Nuestra amplia trayectoria y constante búsqueda de la excelencia nos consolidan como la opción experta y líder en el sector farmacéutico chileno.Promovemos una cultura centrada en la conciliación de la vida personal, familiar y laboral. A través de programas de capacitación, políticas de contratacióninclusivas y oportunidades de desarrollo profesional, buscamos garantizar que todos los miembros de nuestro equipo tengan las herramientas y el apoyo necesarios para alcanzar su máximo potencial.¡Somos Ahumada, tu aliado en salud y bienestar! Importante empresa nacional enfocada en la salud y bienestar se encuentra en búsqueda de Apoyo Logístico para trabajar en nuestros locales ubicados en Colina para cubrir una licencia médica, para realizar labores de inventario, con disposición a mantener el orden y mantención de las dependencias del punto de venta.Este cargo será con contrato por empresa externa.Si te interesa aprender del área de bodega, logística, recepción y despacho ¡Te esperamos!Algunas funciones principales: Recepcionar y revisar la mercadería que llega con el fin de verificar si viene lo que se señala en las guías de despacho y que venga en las condiciones adecuadas para su posterior venta.  Reponer diariamente los productos de las diversas categorías que se exhiben en el punto de venta. Realizar toma y retoma de inventarios, con el objetivo de verificar el stock y mermas de productos que tiene el punto de venta. Actualizar los precios de los productos, con el objetivo de evitar diferencias con respecto al precio que pasará por caja. Realizar limpieza y mantención del orden de todas las dependencias del punto de venta, como espacios comunes como son cocina y baño. Requisitos: - Contar con enseñanza media completa-Tener disponbilidad para trabajar 42 horas semanales distribuidas en turnos rotativos, de lunes a domingo, mañana y tarde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Auxiliar de Farmacia - Las Condes 20 hrs semanales</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Farmacias Ahumada SPA</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Las Condes, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Part-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/auxiliar-de-farmacia-las-condes-20-hrs-semanales-1118372731.html</t>
+        </is>
+      </c>
+      <c r="G375" t="n">
+        <v>0</v>
+      </c>
+      <c r="H375" t="inlineStr"/>
+      <c r="I375" t="n">
+        <v>0</v>
+      </c>
+      <c r="J375" t="n">
+        <v>0</v>
+      </c>
+      <c r="K375" t="n">
+        <v>0</v>
+      </c>
+      <c r="L375" t="n">
+        <v>1</v>
+      </c>
+      <c r="M375" t="n">
+        <v>1</v>
+      </c>
+      <c r="N375" t="n">
+        <v>0</v>
+      </c>
+      <c r="O375" t="n">
+        <v>0</v>
+      </c>
+      <c r="P375" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>Desde nuestra primera apertura en 1969 en la emblemática calle Ahumada de Santiago Centro, hemos crecido y evolucionado para convertirnos en la cadenafarmacéutica chilena con mayor trayectoria del país. Con más de 55 años de historia, Farmacias Ahumada es un referente en el cuidado de la salud en Chile.Nuestro compromiso con la comunidad y la excelencia en el servicio se refleja en nuestras más de 300 farmacias a lo largo del país, respaldadas por más de 2.800 colaboradores, un moderno Centro de Distribución, Oficinas Corporativas y un Recetario Magistral con altos estándares de calidad.Nuestro propósito es claro: ser líderes en el cuidado de las personas. Nos destacamos como expertos en salud, proporcionando una atención integral ypersonalizada a nuestros pacientes para mejorar su calidad de vida y la de sus familias.En esta fase de crecimiento, nos enfocamos en implementar diversas mejoras, enfrentando los nuevos desafíos con foco en nuestros colaboradores y clientes.Fortalecemos nuestro programa de fidelización para brindar soluciones y servicios a más personas, apostando por ofrecer una experiencia consistente en todos los puntos de contacto, desde un e-commerce llamativo y amigable hasta farmacias atractivas y competitivas.Las farmacias y sus colaboradores son el corazón de nuestro negocio. Nos distinguimos por un enfoque centrado en el paciente y un firme compromiso con lasalud y el bienestar de la comunidad. Nuestra amplia trayectoria y constante búsqueda de la excelencia nos consolidan como la opción experta y líder en el sector farmacéutico chileno.Promovemos una cultura centrada en la conciliación de la vida personal, familiar y laboral. A través de programas de capacitación, políticas de contratacióninclusivas y oportunidades de desarrollo profesional, buscamos garantizar que todos los miembros de nuestro equipo tengan las herramientas y el apoyo necesarios para alcanzar su máximo potencial.¡Somos Ahumada, tu aliado en salud y bienestar! Farmacia Ahumada, se encuentra en búsqueda de Auxiliares de Farmacia para unirse a nuestros equipos. Si tienes pasión por el cuidado de la salud, la atención al paciente y quieres formar parte de una empresa con más de 55 años de experiencia en el mercado farmacéutico, ¡esta oportunidad es para ti!Como Auxiliar de Farmacia, reconocido por la SEREMI de Salud, tendrás la importante misión de brindar una atención integral y personalizada a nuestros pacientes, contribuyendo a mejorar su calidad de vida y la de sus familias. Tus funciones principales incluirán asistir en la dispensación de medicamentos, atención al público, gestión de inventario y colaborar en la organización y limpieza de la farmacia.Buscamos personas comprometidas, proactivas y con vocación de servicio, que cuenten con un nivel educativo secundario graduado. La modalidad de trabajo es presencial y en un horario part time sábado y domingo.Te invitamos a participar de las vacantes, excelente nivel de ventas, grato ambiente laboral, ¡locales acondicionados para un mejor desempaño! Vacante en Las Condes para desempeñarse 20 hrs semanales, distribuidos en sábados, domingos y festivos. Requisitos: -Certificado o carnet de Auxiliar de Farmacia otorgado por la SEREMI o Título de Técnico en Farmacia,.-Contar con Enseñanza media completa-Tener disponibilidad para trabajar 20 horas, las cuales se distribuyen entre Sabados, Domingos y Festivos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>AUXILIAR DE FARMACIA - Las Condes 30hrs semanales</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Farmacias Ahumada SPA</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Las Condes, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/auxiliar-de-farmacia-las-condes-30hrs-semanales-1118372730.html</t>
+        </is>
+      </c>
+      <c r="G376" t="n">
+        <v>0</v>
+      </c>
+      <c r="H376" t="inlineStr"/>
+      <c r="I376" t="n">
+        <v>0</v>
+      </c>
+      <c r="J376" t="n">
+        <v>0</v>
+      </c>
+      <c r="K376" t="n">
+        <v>0</v>
+      </c>
+      <c r="L376" t="n">
+        <v>1</v>
+      </c>
+      <c r="M376" t="n">
+        <v>0</v>
+      </c>
+      <c r="N376" t="n">
+        <v>0</v>
+      </c>
+      <c r="O376" t="n">
+        <v>0</v>
+      </c>
+      <c r="P376" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>Desde nuestra primera apertura en 1969 en la emblemática calle Ahumada de Santiago Centro, hemos crecido y evolucionado para convertirnos en la cadenafarmacéutica chilena con mayor trayectoria del país. Con más de 55 años de historia, Farmacias Ahumada es un referente en el cuidado de la salud en Chile.Nuestro compromiso con la comunidad y la excelencia en el servicio se refleja en nuestras más de 300 farmacias a lo largo del país, respaldadas por más de 2.800 colaboradores, un moderno Centro de Distribución, Oficinas Corporativas y un Recetario Magistral con altos estándares de calidad.Nuestro propósito es claro: ser líderes en el cuidado de las personas. Nos destacamos como expertos en salud, proporcionando una atención integral ypersonalizada a nuestros pacientes para mejorar su calidad de vida y la de sus familias.En esta fase de crecimiento, nos enfocamos en implementar diversas mejoras, enfrentando los nuevos desafíos con foco en nuestros colaboradores y clientes.Fortalecemos nuestro programa de fidelización para brindar soluciones y servicios a más personas, apostando por ofrecer una experiencia consistente en todos los puntos de contacto, desde un e-commerce llamativo y amigable hasta farmacias atractivas y competitivas.Las farmacias y sus colaboradores son el corazón de nuestro negocio. Nos distinguimos por un enfoque centrado en el paciente y un firme compromiso con lasalud y el bienestar de la comunidad. Nuestra amplia trayectoria y constante búsqueda de la excelencia nos consolidan como la opción experta y líder en el sector farmacéutico chileno.Promovemos una cultura centrada en la conciliación de la vida personal, familiar y laboral. A través de programas de capacitación, políticas de contratacióninclusivas y oportunidades de desarrollo profesional, buscamos garantizar que todos los miembros de nuestro equipo tengan las herramientas y el apoyo necesarios para alcanzar su máximo potencial.¡Somos Ahumada, tu aliado en salud y bienestar! En Farmacias Ahumada nos encontramos en búsqueda de Auxiliares de Farmacia para nuestra sucursal en Las Condes. Buscamos personas motivadas, proactivas y comprometidas con el cuidado de la salud y el bienestar de nuestros clientes. El/la candidato/a ideal deberá ser capaz de trabajar en equipo, prestar una atención personalizada a los pacientes, gestionar el stock de medicamentos y productos farmacéuticos, entre otras tareas relacionadas con el funcionamiento de la farmacia.Si te apasiona el mundo de la salud, el trabajo en equipo y estás en constante búsqueda de la excelencia, ¡te invitamos a formar parte de nuestro equipo y contribuir a nuestra misión de ser el aliado en salud y bienestar de la comunidad!Necesitamos personas para desempeñarse en jornada de 30 horas semanales distribuidas de lunes a domingo. Requisitos: -Certificado o carnet de Auxiliar de Farmacia otorgado por la SEREMI o Título de Técnico en Farmacia-Contar con enseñanza media completa-Disponibilidad para trabajar 30 horas semalanes distribuidos de lunes a domingo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Apoyo Logístico - Maipú</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Farmacias Ahumada SPA</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Maipú, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/apoyo-logistico-maipu-1118372727.html</t>
+        </is>
+      </c>
+      <c r="G377" t="n">
+        <v>0</v>
+      </c>
+      <c r="H377" t="inlineStr"/>
+      <c r="I377" t="n">
+        <v>0</v>
+      </c>
+      <c r="J377" t="n">
+        <v>0</v>
+      </c>
+      <c r="K377" t="n">
+        <v>0</v>
+      </c>
+      <c r="L377" t="n">
+        <v>1</v>
+      </c>
+      <c r="M377" t="n">
+        <v>0</v>
+      </c>
+      <c r="N377" t="n">
+        <v>0</v>
+      </c>
+      <c r="O377" t="n">
+        <v>0</v>
+      </c>
+      <c r="P377" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>Desde nuestra primera apertura en 1969 en la emblemática calle Ahumada de Santiago Centro, hemos crecido y evolucionado para convertirnos en la cadenafarmacéutica chilena con mayor trayectoria del país. Con más de 55 años de historia, Farmacias Ahumada es un referente en el cuidado de la salud en Chile.Nuestro compromiso con la comunidad y la excelencia en el servicio se refleja en nuestras más de 300 farmacias a lo largo del país, respaldadas por más de 2.800 colaboradores, un moderno Centro de Distribución, Oficinas Corporativas y un Recetario Magistral con altos estándares de calidad.Nuestro propósito es claro: ser líderes en el cuidado de las personas. Nos destacamos como expertos en salud, proporcionando una atención integral ypersonalizada a nuestros pacientes para mejorar su calidad de vida y la de sus familias.En esta fase de crecimiento, nos enfocamos en implementar diversas mejoras, enfrentando los nuevos desafíos con foco en nuestros colaboradores y clientes.Fortalecemos nuestro programa de fidelización para brindar soluciones y servicios a más personas, apostando por ofrecer una experiencia consistente en todos los puntos de contacto, desde un e-commerce llamativo y amigable hasta farmacias atractivas y competitivas.Las farmacias y sus colaboradores son el corazón de nuestro negocio. Nos distinguimos por un enfoque centrado en el paciente y un firme compromiso con lasalud y el bienestar de la comunidad. Nuestra amplia trayectoria y constante búsqueda de la excelencia nos consolidan como la opción experta y líder en el sector farmacéutico chileno.Promovemos una cultura centrada en la conciliación de la vida personal, familiar y laboral. A través de programas de capacitación, políticas de contratacióninclusivas y oportunidades de desarrollo profesional, buscamos garantizar que todos los miembros de nuestro equipo tengan las herramientas y el apoyo necesarios para alcanzar su máximo potencial.¡Somos Ahumada, tu aliado en salud y bienestar! Importante empresa nacional enfocada en la salud y bienestar se encuentra en búsqueda de Apoyo Logístico para trabajar en nuestros locales, para realizar labores de inventario, con disposición a mantener el orden y mantención de las dependencias del punto de venta.Si te interesa aprender del área de bodega, logística, recepción y despacho ¡Te esperamos!Algunas funciones principales: Recepcionar y revisar la mercadería que llega con el fin de verificar si viene lo que se señala en las guías de despacho y que venga en las condiciones adecuadas para su posterior venta.  Reponer diariamente los productos de las diversas categorías que se exhiben en el punto de venta. Realizar toma y retoma de inventarios, con el objetivo de verificar el stock y mermas de productos que tiene el punto de venta. Actualizar los precios de los productos, con el objetivo de evitar diferencias con respecto al precio que pasará por caja. Verificar fechas de vencimiento. Realizar limpieza y mantención del orden de todas las dependencias del punto de venta, como espacios comunes como son cocina y baño. Requisitos: - Contar con enseñanza media completa.-Tener disponbilidad para trabajar 42 horas semanales distribuidas en turnos rotativos, de lunes a domingo, mañana, tarde y noche.</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Subgerente de Personas</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Santiago de Chile, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/subgerente-de-personas-1118372626.html</t>
+        </is>
+      </c>
+      <c r="G378" t="n">
+        <v>3</v>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>modelo</t>
+        </is>
+      </c>
+      <c r="I378" t="n">
+        <v>0</v>
+      </c>
+      <c r="J378" t="n">
+        <v>0</v>
+      </c>
+      <c r="K378" t="n">
+        <v>0</v>
+      </c>
+      <c r="L378" t="n">
+        <v>1</v>
+      </c>
+      <c r="M378" t="n">
+        <v>0</v>
+      </c>
+      <c r="N378" t="n">
+        <v>0</v>
+      </c>
+      <c r="O378" t="n">
+        <v>0</v>
+      </c>
+      <c r="P378" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>Empresa mediana de servicios a la minería requiere incorporar Subgerente de Personas, con reporte directo a la Gerencia de RRHH y un equipo de 4 a 5 personas.La posición está pensada para un(a) profesional que hoy se desempeña como jefe(a) de estas materias y tiene la solidez para asumir una subgerencia. Quien la tome encontrará autonomía amplia, acceso directo a la administración superior y un espacio concreto de desarrollo de carrera.El estilo que buscamos está definido. Alguien que domina la operación porque la ha ejecutado, y que hoy la supervisa con estándar alto. Que forma equipo y delega bien, pero cuando surge un problema llega donde su gerencia con la solución evaluada, no con el problema abierto. Que se mueve con soltura tanto frente a una gerencia de negocios como frente a un trabajador de la operación, y que entiende el escritorio como la mitad del cargo: la otra mitad ocurre en terreno.Responsabilidades del cargo: Supervisar el pago de la nómina de la compañía, garantizando exactitud, cumplimiento de plazos y controles. Supervisar la administración contractual: contratos, anexos y documentación laboral permanentemente al día. Dirigir el control de contratistas y el cumplimiento del régimen de subcontratación. Responder por las acreditaciones laborales ante clientes y organismos, resguardando la continuidad de los servicios. Conducir las relaciones laborales de la empresa: investigaciones bajo Ley Karin, aplicación del modelo disciplinario y administración del Reglamento Interno. Elaborar el presupuesto de mano de obra de la compañía y ejercer su control mensual, junto con el seguimiento del gasto de personal. Diseñar procedimientos e instructivos del área y asegurar su adopción efectiva. Producir la reportería e indicadores que la administración utiliza para decidir.REQUISITOS EXCLUYENTES. Antes de postular, verifica que cumples cada uno de estos puntos; solo esas postulaciones serán consideradas. Experiencia de 12 años o más en administración de personal y relaciones laborales, habiendo operado personalmente los procesos que este cargo supervisa. 5 años o más liderando equipos directos, con evidencia de desarrollo de personas. Supervisión de procesos de nómina y administración contractual en organizaciones de dotación mediana o grande. Control de contratistas bajo régimen de subcontratación y gestión de acreditaciones laborales. Conducción de casos de conflicto laboral, investigaciones de Ley Karin y aplicación de modelo disciplinario y Reglamento Interno. Elaboración de presupuestos de mano de obra y su control, además del seguimiento del gasto de personal. Título universitario de Ingeniería Civil Industrial, Ingeniería Industrial, Ingeniería Comercial o Contador Auditor. El cargo exige una formación que integre base analítica y cuantitativa con gestión, dada su responsabilidad simultánea sobre nómina, presupuesto y equipos. Disponibilidad para desempeño 100% presencial en Santiago Centro, con salidas regulares a las operaciones.IMPORTANTE: esta subgerencia exige haber sido responsable directo de nómina, contratos y relaciones laborales de una dotación propia. Se valorará especialmente experiencia en los siguientes sectores: industrial, servicios a la minería, construcción de obras civiles, ingeniería o energía. La oferta contempla contrato indefinido, renta acorde al nivel de la posición.</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Encargado(a) de Remuneraciones</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Santiago de Chile, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Full-time - Híbrido</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/encargado-a-de-remuneraciones-1118372604.html</t>
+        </is>
+      </c>
+      <c r="G379" t="n">
+        <v>5</v>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>analisis, excel, power bi</t>
+        </is>
+      </c>
+      <c r="I379" t="n">
+        <v>0</v>
+      </c>
+      <c r="J379" t="n">
+        <v>0</v>
+      </c>
+      <c r="K379" t="n">
+        <v>1</v>
+      </c>
+      <c r="L379" t="n">
+        <v>1</v>
+      </c>
+      <c r="M379" t="n">
+        <v>0</v>
+      </c>
+      <c r="N379" t="n">
+        <v>0</v>
+      </c>
+      <c r="O379" t="n">
+        <v>0</v>
+      </c>
+      <c r="P379" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>Empresa chilena del sector de servicios industriales se encuentra en búsqueda de un(a) Encargado(a) de Remuneraciones, responsable de ejecutar de manera integral y autónoma el proceso de cálculo y pago de remuneraciones de la organización.Quien asuma este cargo será el dueño técnico del proceso: recibe las novedades desde las distintas áreas, las revisa y valida contra los respaldos correspondientes antes de procesarlas, ejecuta el cálculo completo y responde por la exactitud y puntualidad del resultado. Se requiere una persona rigurosa, metódica y de conducta profesional intachable, con la solidez para representar observaciones cuando la información recibida no cuenta con el respaldo debido, cualquiera sea el área o nivel que la origine, manteniendo siempre un trato de servicio hacia trabajadores y contrapartes.Objetivos centrales del cargo: proceso de remuneraciones exacto y en plazo, trabajo ordenado y documentado, y avance sostenido en automatización y control.Funciones principales: Cálculo mensual de remuneraciones de principio a fin: haberes fijos y variables, descuentos legales, Previred, impuesto único y cierres. Procesamiento de conceptos variables de alta complejidad: comisiones, bonos, horas extras y sistemas de turnos. Revisión y validación de las novedades informadas por las áreas contra contratos y normativa, previo a su procesamiento. Cálculo de finiquitos y de comisiones asociadas. Tramitación de licencias médicas y de la información de asistencia que alimenta el cálculo. Análisis de cuentas del proceso y centralización contable de remuneraciones, en coordinación con Contabilidad. Automatización de la generación de información, reportes y controles del proceso.REQUISITOS EXCLUYENTES. Te pedimos leer con atención: la postulación será considerada únicamente si cumples la totalidad de los siguientes puntos. Mínimo 7 años de experiencia ejecutando el ciclo completo de remuneraciones. Experiencia procesando nóminas de más de 500 personas. Experiencia demostrable en procesamiento de remuneración variable: comisiones, bonos, horas extras y turnos. Manejo experto de al menos un software de remuneraciones de uso masivo en Chile (Rex+, Talana, Buk u otro equivalente). Conocimiento de análisis de cuentas y centralización contable de remuneraciones. Experiencia validando información de pago proveniente de otras áreas y automatizando procesos de información. Título de Contador Auditor, Contador General, Ingeniería o carrera profesional en Administración o Recursos Humanos, de a lo menos 8 semestres. El cargo integra cálculo de remuneraciones, tributación laboral y registro contable, por lo que su naturaleza exige formación profesional completa en estas disciplinas. Excel avanzado: tablas dinámicas, fórmulas de validación y cruce de bases. Disponibilidad para trabajo presencial en Santiago Centro, con un día semanal de teletrabajo.IMPORTANTE: la función central de este cargo es el cálculo de remuneraciones en toda su extensión. La experiencia concentrada en un solo componente del proceso, en administración de personal sin responsabilidad de cálculo, o desarrollada únicamente en nóminas de baja dotación, corresponde a un alcance distinto del requerido, por lo que no será considerada como experiencia equivalente para este proceso.Se valorará adicionalmente (no excluyente): Experiencia en nómina para empresas de servicio industrial o en servicios de payroll para múltiples clientes. Manejo de Power BI u otras herramientas de reportería y automatización.La contratación contempla un primer contrato a plazo fijo con paso a indefinido conforme a desempeño, tratándose de un cargo permanente y central para la empresa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Especialista Senior en Compensaciones y Beneficios</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Full-time - Híbrido</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/especialista-senior-en-compensaciones-y-beneficios-1118372561.html</t>
+        </is>
+      </c>
+      <c r="G380" t="n">
+        <v>4</v>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>excel, power bi</t>
+        </is>
+      </c>
+      <c r="I380" t="n">
+        <v>0</v>
+      </c>
+      <c r="J380" t="n">
+        <v>0</v>
+      </c>
+      <c r="K380" t="n">
+        <v>1</v>
+      </c>
+      <c r="L380" t="n">
+        <v>1</v>
+      </c>
+      <c r="M380" t="n">
+        <v>0</v>
+      </c>
+      <c r="N380" t="n">
+        <v>0</v>
+      </c>
+      <c r="O380" t="n">
+        <v>0</v>
+      </c>
+      <c r="P380" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>Importante empresa industrial B2B, dedicada a la venta de bienes de capital, con más de 350 colaboradores, busca Especialista Senior en Compensaciones y Beneficios para construir desde cero el subsistema de compensaciones de la organización.Este es un cargo nuevo, de alta visibilidad, que reporta directamente a la Gerencia de RRHH y cuenta con un(a) analista a cargo. No es un rol de administración de remuneraciones ni de payroll: es un rol de diseño técnico, con autonomía real y contraparte directa con las jefaturas del área y con las gerencias de la compañía en calidad de asesor experto.El desafío de los primeros 12 meses es concreto: diseñar la estructura de bandas salariales de la compañía, ordenar la equidad interna, instalar esquemas de renta variable e implementar la reportería y control del gasto de personal.Principales responsabilidades: Valorizar los cargos de la organización aplicando metodología formal y construir la estructura de bandas desde cero. Diagnosticar y corregir brechas de equidad interna, con propuestas accionables para la administración. Diseñar e implementar esquemas de renta variable e incentivos. Construir la reportería de masa salarial y el control de gasto de personal para la toma de decisiones de la alta administración. Gestionar la participación en encuestas de mercado y traducir sus resultados en posicionamiento competitivo. Asesorar a las gerencias y jefaturas de la compañía en decisiones de renta: contrataciones, promociones y ajustes.REQUISITOS EXCLUYENTES. Por favor lee con atención: si no cumples TODOS los puntos siguientes, tu postulación no será considerada. Mínimo 6 años de experiencia específica en compensaciones, dado que el cargo requiere un nivel experto consolidado desde el ingreso. Dominio demostrable de una metodología formal de valoración de cargos (HAY/Korn Ferry, Mercer IPE u otra equivalente) aplicada en proyectos reales, no solo conocimiento teórico. Experiencia construyendo o rediseñando estructuras salariales, no solo administrándolas. Título universitario de Ingeniería Civil Industrial o Ingeniería Comercial, de a lo menos 5 años de duración, con cursos o especialización en compensaciones. La naturaleza analítica y de diseño del cargo requiere formación universitaria completa en estas disciplinas. Excel avanzado real: modelamiento de escenarios de masa salarial, tablas dinámicas. Disponibilidad para trabajar presencialmente en Providencia, con un día de teletrabajo a la semana.IMPORTANTE: este es un rol de diseño técnico de compensaciones (valoración de cargos, estructuras salariales, equidad interna y renta variable). La experiencia en payroll, remuneraciones operativas o administración de personal, siendo valiosa, corresponde a un ámbito distinto al de este cargo, por lo que no será considerada como experiencia equivalente para efectos de este proceso.Deseable (suma puntos, no excluye): Experiencia en empresas industriales o multinacionles. Certificación formal en metodología de valoración de cargos. Manejo de Power BI u otra herramienta de analítica.Ofrecemos contrato a plazo indefinido, un proyecto de construcción técnica con respaldo directo de la Gerencia de RRHH, y la oportunidad de dejar instalado un subsistema completo con tu sello profesional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>TRABAJO REMOTO , SIN EXPERIENCIA</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Full-time - Remoto</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/trabajo-remoto-sin-experiencia-1118372525.html</t>
+        </is>
+      </c>
+      <c r="G381" t="n">
+        <v>0</v>
+      </c>
+      <c r="H381" t="inlineStr"/>
+      <c r="I381" t="n">
+        <v>0</v>
+      </c>
+      <c r="J381" t="n">
+        <v>1</v>
+      </c>
+      <c r="K381" t="n">
+        <v>0</v>
+      </c>
+      <c r="L381" t="n">
+        <v>0</v>
+      </c>
+      <c r="M381" t="n">
+        <v>0</v>
+      </c>
+      <c r="N381" t="n">
+        <v>0</v>
+      </c>
+      <c r="O381" t="n">
+        <v>0</v>
+      </c>
+      <c r="P381" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>TRABAJO REMOTO / SIN EXPERIENCIA URGENTE : Hombres , Mujeres y Jovenes . Chilenos o ExtranjerosCON O SIN EXPERIENCIA EN VENTAS, TRABAJO REMOTO , $290.000 SEMANALES APROXOFRECEMOS HORARIOS FLEXIBLES , CON LA POSIBILIDAD DE RECIBIR INGRESOS DIARIOS, APARTE DEL PAGO QUINCENAL.TE DESARROLLARAS PRINCIPALMENTE EN LAS AREAS DE VENTAS Y SUPERVISIONCONTARAS CON HERRAMIENTAS DIGITALES PARA REALIZAR TELETRABAJO DE FORMA REMOTA EN CUALQUIER LUGAR DE CHILEPOSTULA HOY Y RECIBE INFORMACION DETALLADA, MAS HORARIO DE REUNION VIRTUAL PARA COMENZAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Auxiliar de Limpieza y Lavado - Fábrica Krispy Kreme (Vitacura)</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>PREMIER CAESARS CHILE SPA.</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Vitacura, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/auxiliar-de-limpieza-y-lavado-fabrica-krispy-kreme-vitacura-1118372491.html</t>
+        </is>
+      </c>
+      <c r="G382" t="n">
+        <v>0</v>
+      </c>
+      <c r="H382" t="inlineStr"/>
+      <c r="I382" t="n">
+        <v>0</v>
+      </c>
+      <c r="J382" t="n">
+        <v>0</v>
+      </c>
+      <c r="K382" t="n">
+        <v>0</v>
+      </c>
+      <c r="L382" t="n">
+        <v>1</v>
+      </c>
+      <c r="M382" t="n">
+        <v>0</v>
+      </c>
+      <c r="N382" t="n">
+        <v>0</v>
+      </c>
+      <c r="O382" t="n">
+        <v>0</v>
+      </c>
+      <c r="P382" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>Premier Caesars Chile es una empresa que maneja la franquicia de Little Caesars Pizza y Krispy Kreme para el mercado chileno. La misma forma parte del conglomerado de empresas que posee Grupo Premier, un grupo empresarial Mexicano que contempla restaurantes, agencias automotrices y construcción. En 2013 Grupo Premier obtiene la franquicia de Little Caesars en México, aperturando su primera tienda en Diciembre de dicho año. A fines del 2016, obtiene la única franquicia de Little Caesars para Chile comenzando un agresivo plan de expansión en 2017 a través del desembarco de su filial Premier Caesars Chile. ¡Únete al equipo que endulza Chile! Fábrica Krispy Kreme busca nuevo talento ¿Te imaginas ser pieza clave para que cada doughnut nazca bajo los más altos estándares de calidad? Buscamos un Auxiliar de Limpieza y Lavado para fábrica de Vitacura, la limpieza y el orden no son un detalle: ¡son la base de todo lo que hacemos día a día!Buscamos Auxiliar de Limpieza y Lavado personas comprometidas y con energía para mantener nuestras áreas de producción impecables, resguardando la inocuidad y presentación que nos hacen ser la marca dulce más amada del mundo.Tu rol en la línea de producción: Guardianes de la Higiene: Lavado de bandejas, recipientes, herramientas y equipos menores, asegurando que todo esté listo para la producción. Orden y Excelencia: Limpieza general de superficies y zonas de trabajo, manteniendo los estándares de higiene necesarios para una operación de alto nivel. Continuidad Operativa: Aplicar rutinas de limpieza y sanitización que resguarden el flujo constante de nuestra fábrica. Uso Experto de Insumos: Manejo correcto de elementos de aseo y productos de sanitización según protocolos internos.Jornada:40 horas semanales: Entre 07:00 a 23:00. Requisitos: ¿Qué necesitas para postular? Formación: Enseñanza media completa (requisito obligatorio). Deseable cursos básicos de higiene o manipulación de alimentos. Experiencia: Idealmente 1 año en limpieza industrial, cocina, planta de producción o rubros similares. Conocimientos Técnicos: Manejo básico de normas de higiene e inocuidad en producción de alimentos. Ubicación: Disponibilidad para llegar a nuestra base de operaciones en Vitacura.En Krispy Kreme impulsamos la inclusión. Esta oferta laboral se rige bajo la Ley N° 21.015. Si requieres ajustes razonables para tu postulación, por favor infórmanos.¿Tienes el compromiso necesario para mantener brillando nuestra fábrica? ¡Postula y ayúdanos a endulzar el mundo desde adentro!</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Tornero</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Provincia de Antofagasta, Región II</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/tornero-1118372465.html</t>
+        </is>
+      </c>
+      <c r="G383" t="n">
+        <v>0</v>
+      </c>
+      <c r="H383" t="inlineStr"/>
+      <c r="I383" t="n">
+        <v>0</v>
+      </c>
+      <c r="J383" t="n">
+        <v>0</v>
+      </c>
+      <c r="K383" t="n">
+        <v>0</v>
+      </c>
+      <c r="L383" t="n">
+        <v>1</v>
+      </c>
+      <c r="M383" t="n">
+        <v>0</v>
+      </c>
+      <c r="N383" t="n">
+        <v>0</v>
+      </c>
+      <c r="O383" t="n">
+        <v>0</v>
+      </c>
+      <c r="P383" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>TorneroEmpresa dedicada a la mantención y reparación de motores, generadores y transformadores eléctricos, está en búsqueda de un(a) Tornero para unirse a nuestro equipo.Responsabilidades principales: Manejo de Herramientas de Corte: Dominio de torno, fresadoras Lectura de planos: capacidad para interpretar dibujos técnicos Medición precisa: uso de instrumentos como micrómetros y calibradores para asegurar dimensiones exactas. Conocimientos de materiales: comprensión de las propiedades de diferentes metales y materiales utilizados en el proceso de fabricación. Conocimiento de rodamientos y ajustes, Aritmética. Conocimientos en uso de puente grúa.¿Qué buscamos en ti? Metrólogo, Técnico mecánico o Técnico en máquinas y herramientas Al menos 2 años de experiencia en roles similares Residencia en cuidad de Antofagasta. Disponibilidad para trabajar por turno de lunes a viernes de 8:30 a 17:30 horas.¿Qué te ofrecemos? Contrato a plazo fijo por 2 meses (posibilidad de pasar a indefinido según desempeño). Posibilidades de hacer carrera en la empresa. Sumarte a una empresa estable y en constante crecimiento, con más de 20 años en el mercado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Operador Grua y transpaleta Comuna de Pudahuel</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>TEAM WORK</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Pudahuel, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/operador-grua-y-transpaleta-comuna-de-pudahuel-1118372683.html</t>
+        </is>
+      </c>
+      <c r="G384" t="n">
+        <v>0</v>
+      </c>
+      <c r="H384" t="inlineStr"/>
+      <c r="I384" t="n">
+        <v>0</v>
+      </c>
+      <c r="J384" t="n">
+        <v>0</v>
+      </c>
+      <c r="K384" t="n">
+        <v>0</v>
+      </c>
+      <c r="L384" t="n">
+        <v>1</v>
+      </c>
+      <c r="M384" t="n">
+        <v>0</v>
+      </c>
+      <c r="N384" t="n">
+        <v>0</v>
+      </c>
+      <c r="O384" t="n">
+        <v>0</v>
+      </c>
+      <c r="P384" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>En Team Work nos encontramos en búsqueda de Operador Maquinista con Licencia D para importante empresa Ubicada en Pudahuel Sector Enea.FUNCIONES:Revisión de cargas (productos en pallet a piso) en los diferentes muelles del CD.Cargar y descargar los camiones con la Transpaleta corta y Grua Horquilla Movilizar y mover productos con Transpaleta eléctrica y Grua Horquilla Aseo y orden de la maquinaria, desinfección y seguir los protocolos de higiene.Manejar de forma segura la maquinaria para un correcto funcionamiento del traslado de los productos.Las maquinas a utilizar son:Transpaleta eléctrica uña corta y grua electrica , marca JUNGHEINRICH.REQUISITOS:Licencia Clase D Vigente (excluyente).Experiencia en manejo de Transpaleta eléctrica y grua Disponibilidad para trabajar en turnos rotativos (mañana, tarde y noche).RENTA:Transpaleta(INCLUYE BONO DE PRODUCCIÓN y ASISTENCIA) $699.000 aprox. mensual con disponibilidad de realizar horas extras si se requiere, previa consulta.BENEFICIOS:Colación en casino de la empresa.Buses de acercamiento desde distintas comunas de Santiago.Entrega de uniforme.Horario ROTATIVO: de lunes a sábado en turnos rotativos de mañana, tarde y noche. (42 horas semanales).MAÑANA: de lunes a viernes de 07:30 horas a 15:00 horas y sábado de 7:30 a 17:00 horas.TARDE: lunes a viernes de 14:45 horas a 22:33 horasNOCHE: lunes a viernes de 22:30 horas a 7:45 horas.Beneficios: Con contrato indefinido a partir del 4to mes: Seguro complementario de salud, caja de compensación, posibilidades de crecimiento y desarrollo, utilización y especialización de otras máquinas, buses de acercamiento desde distintas comunas de Santiago, colación, estabilidad laboral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>DE CUALQUIER EDAD - CHILLAN , 506.000 PART TIME</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Chillán, Región XVI</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Part-time - Remoto</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/de-cualquier-edad-chillan-506-000-part-time-1118372663.html</t>
+        </is>
+      </c>
+      <c r="G385" t="n">
+        <v>0</v>
+      </c>
+      <c r="H385" t="inlineStr"/>
+      <c r="I385" t="n">
+        <v>0</v>
+      </c>
+      <c r="J385" t="n">
+        <v>1</v>
+      </c>
+      <c r="K385" t="n">
+        <v>0</v>
+      </c>
+      <c r="L385" t="n">
+        <v>0</v>
+      </c>
+      <c r="M385" t="n">
+        <v>1</v>
+      </c>
+      <c r="N385" t="n">
+        <v>0</v>
+      </c>
+      <c r="O385" t="n">
+        <v>0</v>
+      </c>
+      <c r="P385" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>Buscamos personas de cualquier edad para TRABAJAR EN VENTAS con modalidad REMOTO PART TIME, dedicando desde 3 horas al diaLas ventas se realizan a traves de Pagina web (gratuita) y contamos con envios gratuitos a todo el pais .Recibiras:Sitio web personal. (gratuito)App Movil (opcional)Call center gratuito para ti y tus clientesEntrenamientos virtuales semanales constantesWhatsapp de la empresa con apoyo constanteBono el primer dia y ademas mensuales en dinero por cumplimiento de metas*Tenemos formato PART-TIME especial para estudiantes o personas que necesitan un segundo ingreso o trabajar desde su casa.Postula ahora y accede a la informacion detallada y cita para reunion virtual</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>EMPRESA NECESITA PERSONAS- URGENTE</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Santiago de Chile, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Part-time - Remoto</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/empresa-necesita-personas-urgente-1118372662.html</t>
+        </is>
+      </c>
+      <c r="G386" t="n">
+        <v>0</v>
+      </c>
+      <c r="H386" t="inlineStr"/>
+      <c r="I386" t="n">
+        <v>0</v>
+      </c>
+      <c r="J386" t="n">
+        <v>1</v>
+      </c>
+      <c r="K386" t="n">
+        <v>0</v>
+      </c>
+      <c r="L386" t="n">
+        <v>0</v>
+      </c>
+      <c r="M386" t="n">
+        <v>1</v>
+      </c>
+      <c r="N386" t="n">
+        <v>0</v>
+      </c>
+      <c r="O386" t="n">
+        <v>0</v>
+      </c>
+      <c r="P386" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>URGENTE PARA CASA REGION DE CHILE , POR LA APERTURA DE NUEVOS MERCADOS, EMPRESA NECESITA PERSONAS MOTIVADAS DESDE 18 AÑOS , CON MANEJO DE REDES SOCIALESSOLICITAMOS CON O SIN EXPERIENCIA , PRINCIPALMENTE PARA EL AREA DE VENTAS.HORARIOS FLEXIBLES (PART TIME) GANANCIAS DIARIAS Y QUINCENALESTRABAJA DESDE TU TELEFONO O COMPUTADOR, DESDE CUALQUIER LUGAR EN 21 PAISES DIFERENTESOBTENDRAS HERRAMIENTAS DIGITALES:  PAGINA WEB (gratis)  APP PROPIA (opcional)  COACHING VIRTUAL 3 VECES POR SEMANA GRATUITOPOSTULA AHORAGANANCIAS APROXIMADAS $448.000 A $506.000 CON HORARIOS LIBRES</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Operarios-as multifucionales Mcdonalds Mall Plaza Oeste</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Adm. De Franquicias Carrasco y compañía LTDA.</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Cerrillos , Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Por Horas - Presencial</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/operarios-as-multifucionales-mcdonalds-mall-plaza-oeste-1118372644.html</t>
+        </is>
+      </c>
+      <c r="G387" t="n">
+        <v>0</v>
+      </c>
+      <c r="H387" t="inlineStr"/>
+      <c r="I387" t="n">
+        <v>0</v>
+      </c>
+      <c r="J387" t="n">
+        <v>0</v>
+      </c>
+      <c r="K387" t="n">
+        <v>0</v>
+      </c>
+      <c r="L387" t="n">
+        <v>1</v>
+      </c>
+      <c r="M387" t="n">
+        <v>0</v>
+      </c>
+      <c r="N387" t="n">
+        <v>0</v>
+      </c>
+      <c r="O387" t="n">
+        <v>0</v>
+      </c>
+      <c r="P387" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>McDonald's se encuentra actualmente en busca de operarios multifuncionales para su local ubicado en el Mall Plaza Oeste, a realizar funciones múltiples y rotativas como: atendención de clientes, manipulación de alimentos, producción de alimentos, bodegaje, limpieza, entre otras.Tenemos jornadas con horarios flexibles desde las 16 hasta las 30 horas semanales, idealmente para compatibilizar estudios y trabajo.Nuestro Candidato Ideal: -Mayor de 18 años (excluyente) -Estudiantes-No es necesaria experiencia previa. Ubicación: Mall Plaza OesteBeneficios: Colación Transporte en horarios de cierre Caja de compensación Capacitación constante Horarios flexibles Entre otrosOfrecemos entrenamiento simple, fácil y rápido. Un ambiente juvenil, y posibilidades de crecer dentro de la compañía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Encargado(a) de Administración de Personal</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Full-time - Híbrido</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/encargado-a-de-administracion-de-personal-1118372614.html</t>
+        </is>
+      </c>
+      <c r="G388" t="n">
+        <v>2</v>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I388" t="n">
+        <v>0</v>
+      </c>
+      <c r="J388" t="n">
+        <v>0</v>
+      </c>
+      <c r="K388" t="n">
+        <v>1</v>
+      </c>
+      <c r="L388" t="n">
+        <v>1</v>
+      </c>
+      <c r="M388" t="n">
+        <v>0</v>
+      </c>
+      <c r="N388" t="n">
+        <v>0</v>
+      </c>
+      <c r="O388" t="n">
+        <v>0</v>
+      </c>
+      <c r="P388" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>Empresa nacional de servicios industriales requiere incorporar un(a) Encargado(a) de Administración de Personal, con reporte a la Subgerencia de Recursos Humanos.El propósito del cargo es simple de enunciar y exigente de cumplir: que la documentación contractual de toda la dotación esté permanentemente al día y que la información de asistencia llegue a remuneraciones completa, validada y en plazo, todos los meses, sin excepción. Es un cargo que se gestiona por calendario de vencimientos, indicadores y fechas legales, por lo que buscamos a alguien metódico, disciplinado y acostumbrado a trabajar por KPIs y tiempos comprometidos, con buen trato y vocación de servicio hacia las áreas y los trabajadores.Sus responsabilidades: Mantener al día los contratos de trabajo de toda la dotación y confeccionar los anexos correspondientes, controlando vencimientos y renovaciones dentro de los plazos legales. Dar soporte a las jefaturas y áreas de la compañía en materias contractuales, de reglamento interno y de procedimientos. Administrar el control de asistencia: revisión de marcas, turnos y novedades de la dotación. Preparar y entregar a remuneraciones, en los plazos de cierre definidos, la información validada de horas extras, atrasos e inasistencias para su correcto pago o descuento. Regularizar y mantener el orden del archivo documental laboral, asegurando su trazabilidad ante fiscalizaciones. Reportar KPIs de su gestión: contratos vigentes, anexos en plazo, calidad y oportunidad de la información de asistencia.REQUISITOS EXCLUYENTES. Solo serán consideradas las postulaciones que cumplan la totalidad de estos puntos, por lo que te pedimos revisarlos con detención antes de postular. Experiencia mínima de 7 años gestionando en forma simultánea documentación contractual (contratos y anexos) y control de asistencia, dado que el cargo integra ambos frentes. Experiencia administrando dotaciones de más de 600 trabajadores. Manejo de sistemas de control de asistencia y relojes control, incluyendo dotaciones con turnos. Conocimiento aplicado de legislación laboral en materia de contratos, jornadas y reglamento interno. Experiencia trabajando con metas, KPIs y plazos de cierre mensual. Formación profesional de a lo menos 8 semestres en Administración, Recursos Humanos, Ingeniería, Contabilidad o Derecho. El cargo exige interpretar y aplicar normativa laboral y contractual, lo que requiere formación profesional completa en estas disciplinas. Excel avanzado: tablas dinámicas y cruces de bases para validación de asistencia. Disponibilidad para trabajo presencial en Providencia, con un día de teletrabajo semanal.IMPORTANTE: el cargo requiere dominio simultáneo de los dos frentes descritos, documentación contractual y control de asistencia, adquirido en organizaciones de dotación mediana o grande. La experiencia desarrollada en un solo frente, en dotaciones pequeñas, en cálculo de remuneraciones, o el ejercicio del Derecho orientado a litigios, corresponden a alcances distintos del requerido, por lo que no serán consideradas experiencias equivalentes para este proceso.La incorporación contempla un primer contrato a plazo fijo con paso a indefinido según desempeño (se puede evaluar esta condición), en un cargo permanente dentro de la estructura de la compañía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Auditor de Calidad</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Entel Call Center S A</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/auditor-de-calidad-1118372458.html</t>
+        </is>
+      </c>
+      <c r="G389" t="n">
+        <v>0</v>
+      </c>
+      <c r="H389" t="inlineStr"/>
+      <c r="I389" t="n">
+        <v>0</v>
+      </c>
+      <c r="J389" t="n">
+        <v>0</v>
+      </c>
+      <c r="K389" t="n">
+        <v>0</v>
+      </c>
+      <c r="L389" t="n">
+        <v>1</v>
+      </c>
+      <c r="M389" t="n">
+        <v>0</v>
+      </c>
+      <c r="N389" t="n">
+        <v>0</v>
+      </c>
+      <c r="O389" t="n">
+        <v>0</v>
+      </c>
+      <c r="P389" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>Somos Entel ConnectNuestro propósito es ayudar a transformar la experiencia de los usuarios, integrando tecnologías, procesos y personas cercanas, aportando al desarrollo de tu negocio y la sociedad. Buscamos personas que sientan como su cliente, que inspire y movilice, liderando los cambios con excelencia en sus resultados.Misión del cargo: Monitorear la calidad de atención brindada por los ejecutivos a los usuarios finales, para elaborar planes de acción a  las falencias¡La empresa de telefonía más grande de Sudamérica busca tu talento!Entel Connect Center está interesada en ti y buscamos:* Técnico trunco o en curso de computación, administración o carreras afines.* Contar con 1 años de experiencia mínimo en el rubro.¿Qué harás?1. Evaluar la calidad de atención (contacto) y medir la capacidad de resolución de los ejecutivos durante la gestión de llamadas entrantes y salientes a los usuarios finales de nuestros clientes, identificando los errores en base a pautas de calidad, para corregir falencias y retroalimentar a la operación con el fin de mejorar su desempeño. 2. Monitorear llamadas que han sido evaluadas por los usuarios (EPA o NPS en los servicios que apliquen).3. Realizar la verificación de habilidades mínimas de los postulantes a los servicios (Examen escrito, Role Play u OJT) para determinar si están aptos para desempeñarse como ejecutivos.4. Brindar feedback a los ejecutivos, sobre los resultados de los monitoreos y evaluaciones y en otros casos brindar información necesaria a los supervisores para el feedback a los ejecutivos. (Dependerá del servicio)5. Elaboración de cuadro de ranking de calidad de los ejecutivos, por supervisor y del servicio, así como los errores detectados en las evaluaciones.6. Analizar la información de las evaluaciones, para elaborar planes de acción y seguimiento con el objetivo de obtener mejoras en la gestión.7. Realizar reuniones de calibración de la pauta de Calidad con involucrados en el proceso.8. Participar de capacitaciones durante la implementación de nuevos servicios o ante cambios y/o modificaciones de servicios en operación.9. Cumplir con las políticas y reglamento de SST de la empresa.10. Realizar cualquier otra actividad inherente a su cargo, así como las que le asigne su superior inmediato¿Qué te ofrecemos?Sueldo superior al mercado.Oportunidad de desarrollo profesional y línea de carrera.Excelente clima laboral.Nuestro Candidato Ideal:Experiencia Call centerExperiencia supervisando equiposExperiencia auditando calidadUbicación: Huechuraba, MetropolitanaDiscapacidad: Esta vacante es apta para personas con discapacidad.El proceso de selección se realiza a través de Aira - plataforma de reclutamiento diseñado para mejorar tu experiencia de postulación.        Para postular solo necesitas:        1. Postular a la oferta        2. Revisar tu email        3. Ingresar a Aira y contestar las preguntas y/o pruebas solicitadas        Luego, si vemos que tu perfil se ajusta a lo que estamos buscando, te contactaremos por...(Más información al postular)</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Asistente de Marketing</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Soluparts Ltda</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>La Cisterna, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/asistente-de-marketing-1118372572.html</t>
+        </is>
+      </c>
+      <c r="G390" t="n">
+        <v>0</v>
+      </c>
+      <c r="H390" t="inlineStr"/>
+      <c r="I390" t="n">
+        <v>0</v>
+      </c>
+      <c r="J390" t="n">
+        <v>0</v>
+      </c>
+      <c r="K390" t="n">
+        <v>0</v>
+      </c>
+      <c r="L390" t="n">
+        <v>1</v>
+      </c>
+      <c r="M390" t="n">
+        <v>0</v>
+      </c>
+      <c r="N390" t="n">
+        <v>0</v>
+      </c>
+      <c r="O390" t="n">
+        <v>0</v>
+      </c>
+      <c r="P390" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>Asistente de Marketing Resumen del Puesto Buscamos un Asistente de Marketing creativo, dinámico y con orientación comercial para fortalecer nuestra imagen y presencia digital. El candidato ideal poseerá habilidades de diseño y gestión de redes sociales, con un enfoque en la generación de contenido atractivo y el apoyo a campañas comerciales. Responsabilidades  Crear contenido atractivo para redes sociales. Diseñar gráficas, promociones y material corporativo. Apoyar campañas comerciales y acciones para impulsar las ventas. Coordinar publicaciones y mantener actualizadas las plataformas digitales. Realizar seguimiento de resultados e interacción en redes sociales.  Requisitos  Manejo de herramientas de diseño gráfico como Canva. Conocimientos en la gestión de redes sociales (Instagram, Facebook, TikTok, etc.). Conocimientos básicos de edición de fotografías y videos. Perfil comercial y orientación a resultados. Creatividad para desarrollar contenido, promociones y material publicitario. Excelente redacción y ortografía. Organización, iniciativa, responsabilidad y capacidad para trabajar en equipo. Se valorará experiencia previa en marketing digital o cargos similares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Conductor Profesional</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>TU DESTNO SEGURO C.A</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Villarrica, Región IX</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/conductor-profesional-1118357143.html</t>
+        </is>
+      </c>
+      <c r="G391" t="n">
+        <v>0</v>
+      </c>
+      <c r="H391" t="inlineStr"/>
+      <c r="I391" t="n">
+        <v>0</v>
+      </c>
+      <c r="J391" t="n">
+        <v>0</v>
+      </c>
+      <c r="K391" t="n">
+        <v>0</v>
+      </c>
+      <c r="L391" t="n">
+        <v>1</v>
+      </c>
+      <c r="M391" t="n">
+        <v>0</v>
+      </c>
+      <c r="N391" t="n">
+        <v>0</v>
+      </c>
+      <c r="O391" t="n">
+        <v>0</v>
+      </c>
+      <c r="P391" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>Conductor Profesional Resumen del Puesto Estamos en la búsqueda de un Conductor Profesional con experiencia y una actitud proactiva para integrarse a nuestro equipo. El candidato ideal deberá demostrar un historial de conducción segura y responsable, así como una gran disposición para el trabajo. Responsabilidades  Operar vehículos de manera segura y eficiente. Cumplir con los horarios y rutas establecidas. Realizar verificaciones básicas del vehículo antes y después de cada servicio. Mantener una comunicación fluida con el equipo de operaciones. Asegurar la correcta manipulación y transporte de la carga o pasajeros.  Requisitos  Licencia de conducir vigente y en regla. Experiencia comprobable en conducción profesional. Conocimiento de normativas de tránsito. Excelente historial de conducción. Capacidad para trabajar de forma autónoma y con responsabilidad. Disponibilidad y compromiso con las tareas asignadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Garzón y Encargado de Cocina Part-Time</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Daniela Solis</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Santiago de Chile, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/garzon-y-encargado-de-cocina-part-time-1118372628.html</t>
+        </is>
+      </c>
+      <c r="G392" t="n">
+        <v>0</v>
+      </c>
+      <c r="H392" t="inlineStr"/>
+      <c r="I392" t="n">
+        <v>0</v>
+      </c>
+      <c r="J392" t="n">
+        <v>0</v>
+      </c>
+      <c r="K392" t="n">
+        <v>0</v>
+      </c>
+      <c r="L392" t="n">
+        <v>1</v>
+      </c>
+      <c r="M392" t="n">
+        <v>1</v>
+      </c>
+      <c r="N392" t="n">
+        <v>1</v>
+      </c>
+      <c r="O392" t="n">
+        <v>0</v>
+      </c>
+      <c r="P392" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>Garzón y Encargado de Cocina Part-Time Resumen del Puesto Estamos en la búsqueda de un Garzón y Encargado de Cocina Part-Time dinámico y con experiencia para unirse a nuestro equipo. El candidato ideal poseerá habilidades tanto en el servicio al cliente como en la preparación de alimentos, con capacidad para gestionar eficientemente las operaciones de cocina en un entorno de banquetería. Responsabilidades  Atender a los clientes de manera cordial y eficiente, tomando pedidos y sirviendo alimentos y bebidas. Colaborar en la preparación de menús y platos para eventos, asegurando la calidad y presentación. Supervisar las tareas de cocina, garantizando el cumplimiento de los estándares de higiene y seguridad alimentaria. Gestionar el inventario de insumos de cocina y realizar pedidos según sea necesario. Mantener la limpieza y el orden en todas las áreas de trabajo. Adaptarse a las necesidades específicas de cada evento, ya sea corporativo o personal.  Requisitos  Experiencia previa comprobable en roles de garzón y/o encargado de cocina. Conocimiento de técnicas culinarias básicas y buenas prácticas de manipulación de alimentos. Habilidades de servicio al cliente y excelente trato interpersonal. Capacidad para trabajar bajo presión y en un entorno dinámico. Flexibilidad horaria para cubrir turnos part-time, incluyendo fines de semana y festivos. Proactividad y capacidad para trabajar en equipo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Operario de Producción</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Vitalcom</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Recoleta, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/operario-de-produccion-1118372457.html</t>
+        </is>
+      </c>
+      <c r="G393" t="n">
+        <v>0</v>
+      </c>
+      <c r="H393" t="inlineStr"/>
+      <c r="I393" t="n">
+        <v>0</v>
+      </c>
+      <c r="J393" t="n">
+        <v>0</v>
+      </c>
+      <c r="K393" t="n">
+        <v>0</v>
+      </c>
+      <c r="L393" t="n">
+        <v>1</v>
+      </c>
+      <c r="M393" t="n">
+        <v>0</v>
+      </c>
+      <c r="N393" t="n">
+        <v>0</v>
+      </c>
+      <c r="O393" t="n">
+        <v>0</v>
+      </c>
+      <c r="P393" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>Operario de Producción Resumen del Puesto Buscamos un Operario de Producción responsable y comprometido para unirse a nuestro equipo en una empresa en crecimiento. El candidato ideal será una persona puntual, proactiva y con ganas de desarrollarse profesionalmente. Responsabilidades  Participar en las tareas de producción y control de calidad en planta. Colaborar en el control y registro de inventario de materias primas. Mantener el orden, la limpieza y la trazabilidad en las áreas de producción.  Requisitos  Enseñanza media completa. Experiencia previa en planta es deseable, pero no excluyente. Habilidades de puntualidad, responsabilidad y proactividad.  Ofrecemos  Contrato formal desde el primer día. Remuneración acorde al mercado y beneficios legales. Un buen ambiente laboral. Oportunidades de crecimiento profesional.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/laborum/summary_data.xlsx
+++ b/data/laborum/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q393"/>
+  <dimension ref="A1:Q423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26431,6 +26431,1972 @@
         </is>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>ENFERMERAS O TENS, DESDE 3 HRS AL DIA- TODO CHILE</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Santiago de Chile, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Por Horas - Remoto</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/enfermeras-o-tens-desde-3-hrs-al-dia-todo-chile-1118372785.html</t>
+        </is>
+      </c>
+      <c r="G394" t="n">
+        <v>0</v>
+      </c>
+      <c r="H394" t="inlineStr"/>
+      <c r="I394" t="n">
+        <v>0</v>
+      </c>
+      <c r="J394" t="n">
+        <v>1</v>
+      </c>
+      <c r="K394" t="n">
+        <v>0</v>
+      </c>
+      <c r="L394" t="n">
+        <v>0</v>
+      </c>
+      <c r="M394" t="n">
+        <v>1</v>
+      </c>
+      <c r="N394" t="n">
+        <v>0</v>
+      </c>
+      <c r="O394" t="n">
+        <v>0</v>
+      </c>
+      <c r="P394" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>ENFERMERAS DESDE 3 HORAS AL DIA / TODO CHILETRABAJO REMOTO PART TIME PARA ENFERMEROS, TENS, KINESIOLOGOS , NUTRICIONISTAS Y TERAPIA OCUPACIONALBUSCAMOS PERSONAS PARA TRABAJAR EN VENTAS , DEDICANDO DESDE 3 HORAS AL DIATE ENSEÑAREMOS DESDE CERO , SI NO CUENTAS AUN CON EXPERIENCIARECIBIRAS:SITIO WEB PERSONAL (gratis)APLICACION MOVIL (opcional)APOYO CALL CENTER MUNDIAL linea 800ENVIOS A TODO CHILE , CON CONVENIO CON 3 EMPRESAS DE ENVIO Y SEGUIMIENTO VIA WEB O CALL CENTERCAPACITACIONES CONSTANTES, SEMANALES DE MANERA VIRTUALEL FORMATO PART-TIME ES ESPECIAL PARA PROFESIONALES DE LA SALUD QUE NECESITEN UN INGRESO EXTRA O TRABAJAR ALGUNAS HORAS DESDE CASAPOSTULA HOY Y ACCEDE A REUNIÓN VIRTUAL EN LA SEMANAENVIAREMOS INFORMACION DETALLADA A SU CORREO</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Apoyo Logístico - Huechuraba</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Farmacias Ahumada SPA</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Huechuraba, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/apoyo-logistico-huechuraba-1118372772.html</t>
+        </is>
+      </c>
+      <c r="G395" t="n">
+        <v>0</v>
+      </c>
+      <c r="H395" t="inlineStr"/>
+      <c r="I395" t="n">
+        <v>0</v>
+      </c>
+      <c r="J395" t="n">
+        <v>0</v>
+      </c>
+      <c r="K395" t="n">
+        <v>0</v>
+      </c>
+      <c r="L395" t="n">
+        <v>1</v>
+      </c>
+      <c r="M395" t="n">
+        <v>0</v>
+      </c>
+      <c r="N395" t="n">
+        <v>0</v>
+      </c>
+      <c r="O395" t="n">
+        <v>0</v>
+      </c>
+      <c r="P395" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>Desde nuestra primera apertura en 1969 en la emblemática calle Ahumada de Santiago Centro, hemos crecido y evolucionado para convertirnos en la cadenafarmacéutica chilena con mayor trayectoria del país. Con más de 56 años de historia, Farmacias Ahumada es un referente en el cuidado de la salud en Chile.Nuestro compromiso con la comunidad y la excelencia en el servicio se refleja en nuestras más de 400 farmacias a lo largo del país, respaldadas por más de 2.800 colaboradores, un moderno Centro de Distribución, Oficinas Corporativas y un Recetario Magistral con altos estándares de calidad.Nuestro propósito es claro: ser líderes en el cuidado de las personas. Nos destacamos como expertos en salud, proporcionando una atención integral ypersonalizada a nuestros pacientes para mejorar su calidad de vida y la de sus familias.En esta fase de crecimiento, nos enfocamos en implementar diversas mejoras, enfrentando los nuevos desafíos con foco en nuestros colaboradores y clientes.Fortalecemos nuestro programa de fidelización para brindar soluciones y servicios a más personas, apostando por ofrecer una experiencia consistente en todos los puntos de contacto, desde un e-commerce llamativo y amigable hasta farmacias atractivas y competitivas.Las farmacias y sus colaboradores son el corazón de nuestro negocio. Nos distinguimos por un enfoque centrado en el paciente y un firme compromiso con lasalud y el bienestar de la comunidad. Nuestra amplia trayectoria y constante búsqueda de la excelencia nos consolidan como la opción experta y líder en el sector farmacéutico chileno.Promovemos una cultura centrada en la conciliación de la vida personal, familiar y laboral. A través de programas de capacitación, políticas de contratacióninclusivas y oportunidades de desarrollo profesional, buscamos garantizar que todos los miembros de nuestro equipo tengan las herramientas y el apoyo necesarios para alcanzar su máximo potencial.¡Somos Ahumada, tu aliado en salud y bienestar! Importante empresa nacional enfocada en la salud y bienestar se encuentra en búsqueda de Apoyo Logístico para trabajar en nuestros locales ubicados en Huechuraba, para realizar labores de inventario, con disposición a mantener el orden y mantención de las dependencias del punto de venta.Este cargo será con contrato por empresa externa.Si te interesa aprender del área de bodega, logística, recepción y despacho ¡Te esperamos!Algunas funciones principales: Recepcionar y revisar la mercadería que llega con el fin de verificar si viene lo que se señala en las guías de despacho y que venga en las condiciones adecuadas para su posterior venta.  Reponer diariamente los productos de las diversas categorías que se exhiben en el punto de venta. Realizar toma y retoma de inventarios, con el objetivo de verificar el stock y mermas de productos que tiene el punto de venta. Actualizar los precios de los productos, con el objetivo de evitar diferencias con respecto al precio que pasará por caja. Realizar limpieza y mantención del orden de todas las dependencias del punto de venta, como espacios comunes como son cocina y baño. Requisitos: - Contar con enseñanza media completa-Tener disponbilidad para trabajar 42 horas semanales distribuidas en turnos rotativos, de lunes a domingo, mañana y tarde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Auxiliar de Farmacia - Lo Barnechea-Full time</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Farmacias Ahumada SPA</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Lo Barnechea, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/auxiliar-de-farmacia-lo-barnechea-full-time-1118372770.html</t>
+        </is>
+      </c>
+      <c r="G396" t="n">
+        <v>0</v>
+      </c>
+      <c r="H396" t="inlineStr"/>
+      <c r="I396" t="n">
+        <v>0</v>
+      </c>
+      <c r="J396" t="n">
+        <v>0</v>
+      </c>
+      <c r="K396" t="n">
+        <v>0</v>
+      </c>
+      <c r="L396" t="n">
+        <v>1</v>
+      </c>
+      <c r="M396" t="n">
+        <v>0</v>
+      </c>
+      <c r="N396" t="n">
+        <v>0</v>
+      </c>
+      <c r="O396" t="n">
+        <v>0</v>
+      </c>
+      <c r="P396" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>Desde nuestra primera apertura en 1969 en la emblemática calle Ahumada de Santiago Centro, hemos crecido y evolucionado para convertirnos en la cadenafarmacéutica chilena con mayor trayectoria del país. Con más de 56 años de historia, Farmacias Ahumada es un referente en el cuidado de la salud en Chile.Nuestro compromiso con la comunidad y la excelencia en el servicio se refleja en nuestras más de 400 farmacias a lo largo del país, respaldadas por más de 2.800 colaboradores, un moderno Centro de Distribución, Oficinas Corporativas y un Recetario Magistral con altos estándares de calidad.Nuestro propósito es claro: ser líderes en el cuidado de las personas. Nos destacamos como expertos en salud, proporcionando una atención integral ypersonalizada a nuestros pacientes para mejorar su calidad de vida y la de sus familias.En esta fase de crecimiento, nos enfocamos en implementar diversas mejoras, enfrentando los nuevos desafíos con foco en nuestros colaboradores y clientes.Fortalecemos nuestro programa de fidelización para brindar soluciones y servicios a más personas, apostando por ofrecer una experiencia consistente en todos los puntos de contacto, desde un e-commerce llamativo y amigable hasta farmacias atractivas y competitivas.Las farmacias y sus colaboradores son el corazón de nuestro negocio. Nos distinguimos por un enfoque centrado en el paciente y un firme compromiso con lasalud y el bienestar de la comunidad. Nuestra amplia trayectoria y constante búsqueda de la excelencia nos consolidan como la opción experta y líder en el sector farmacéutico chileno.Promovemos una cultura centrada en la conciliación de la vida personal, familiar y laboral. A través de programas de capacitación, políticas de contratacióninclusivas y oportunidades de desarrollo profesional, buscamos garantizar que todos los miembros de nuestro equipo tengan las herramientas y el apoyo necesarios para alcanzar su máximo potencial.¡Somos Ahumada, tu aliado en salud y bienestar! En Farmacias Ahumada nos encontramos en búsqueda de Auxiliares de Farmacia para nuestra sucursal en Lo Barnechea jornada completa. Buscamos a una persona motivada, proactiva y comprometida con el cuidado de la salud y el bienestar de nuestros clientes. El/la candidato/a ideal deberá ser capaz de trabajar en equipo, prestar una atención personalizada a los pacientes, gestionar el stock de medicamentos y productos farmacéuticos, entre otras tareas relacionadas con el funcionamiento de la farmacia.En esta posición, tendrás la oportunidad de formar parte de una empresa con más de 56 años de trayectoria en el sector farmacéutico chileno, que se destaca por su compromiso con la comunidad, la excelencia en el servicio y la atención integral a sus clientes. Nuestro propósito es claro: ser líderes en el cuidado de las personas, brindando soluciones y servicios que mejoren la calidad de vida de nuestros pacientes y sus familias.Si te apasiona el mundo de la salud, el trabajo en equipo y estás en constante búsqueda de la excelencia, ¡te invitamos a formar parte de nuestro equipo y contribuir a nuestra misión de ser el aliado en salud y bienestar de la comunidad!En Farmacias Ahumada nos encontramos en busca de Auxiliares de Farmacia para nuestra sucursal en Lo Barnechea.Si eres Auxiliar de Farmacia y te caracterizas por tu vocación de servicio y experiencia, ayúdanos a brindar a nuestros clientes la asesoría y el cuidado que necesitan, entregando un mayor acceso a la salud. ¡Te esperamos! ¿Qué tendrás que hacer? -Realizar el proceso de atención y venta al cliente.-Derivar todas las consultas farmacológicas al Químico Farmacéutico de turno, como también las solicitudes de devolución o cambios de productos.-Revisar y reponer diariamente productos en las estanterías.-Llevar el control diario de las fechas de vencimiento de los productos.-Participar activamente de todos los inventarios. Requisitos: -Certificado o carnet de Auxiliar de Farmacia otorgado por la SEREMI o Título de Técnico en Farmacia-Contar con enseñanza media completa-Disponibilidad para trabajar de lunes a domingo, 42 horas semanales, en turnos rotartiovs mañana y tarde, con un día libre a la semana. Con 2 domingos libres al mes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Category Planner</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Farmacias Ahumada SPA</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Huechuraba, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/category-planner-1118372761.html</t>
+        </is>
+      </c>
+      <c r="G397" t="n">
+        <v>3</v>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>analisis, excel</t>
+        </is>
+      </c>
+      <c r="I397" t="n">
+        <v>0</v>
+      </c>
+      <c r="J397" t="n">
+        <v>0</v>
+      </c>
+      <c r="K397" t="n">
+        <v>0</v>
+      </c>
+      <c r="L397" t="n">
+        <v>1</v>
+      </c>
+      <c r="M397" t="n">
+        <v>0</v>
+      </c>
+      <c r="N397" t="n">
+        <v>0</v>
+      </c>
+      <c r="O397" t="n">
+        <v>0</v>
+      </c>
+      <c r="P397" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>Desde nuestra primera apertura en 1969 en la emblemática calle Ahumada de Santiago Centro, hemos crecido y evolucionado para convertirnos en la cadenafarmacéutica chilena con mayor trayectoria del país. Con más de 56 años de historia, Farmacias Ahumada es un referente en el cuidado de la salud en Chile.Nuestro compromiso con la comunidad y la excelencia en el servicio se refleja en nuestras más de 400 farmacias a lo largo del país, respaldadas por más de 3.000 colaboradores, un moderno Centro de Distribución, Oficinas Corporativas y un Recetario Magistral con altos estándares de calidad.Nuestro propósito es claro: ser líderes en el cuidado de las personas. Nos destacamos como expertos en salud, proporcionando una atención integral ypersonalizada a nuestros pacientes para mejorar su calidad de vida y la de sus familias.En esta fase de crecimiento, nos enfocamos en implementar diversas mejoras, enfrentando los nuevos desafíos con foco en nuestros colaboradores y clientes.Fortalecemos nuestro programa de fidelización para brindar soluciones y servicios a más personas, apostando por ofrecer una experiencia consistente en todos los puntos de contacto, desde un e-commerce llamativo y amigable hasta farmacias atractivas y competitivas.Las farmacias y sus colaboradores son el corazón de nuestro negocio. Nos distinguimos por un enfoque centrado en el paciente y un firme compromiso con lasalud y el bienestar de la comunidad. Nuestra amplia trayectoria y constante búsqueda de la excelencia nos consolidan como la opción experta y líder en el sector farmacéutico chileno.Promovemos una cultura centrada en la conciliación de la vida personal, familiar y laboral. A través de programas de capacitación, políticas de contratacióninclusivas y oportunidades de desarrollo profesional, buscamos garantizar que todos los miembros de nuestro equipo tengan las herramientas y el apoyo necesarios para alcanzar su máximo potencial.¡Somos Ahumada, tu aliado en salud y bienestar! ¡Te invitamos a protagonizar la evolución del cuidado de la salud en Chile!En Farmacias Ahumada buscamos incorporar a un(a) Category Planner para formar parte de nuestra Gerencia Comercial, desempeñando un rol clave en la optimización de espacios, la estrategia de surtido y la experiencia de compra de nuestros clientes.Si te apasiona el análisis de datos, la planificación comercial y la gestión de categorías, esta es una excelente oportunidad para desarrollar tu carrera en una compañía con más de 56 años de trayectoria e innovación en el mercado.Misión del cargoOptimizar la planificación y administración de los espacios destinados a la exhibición de los productos, asegurando una correcta ejecución de planogramas y contribuyendo, en conjunto con las áreas Comercial y Category Management, a la definición del surtido y segmentación de categorías que maximicen las ventas y la experiencia de nuestros clientes.¿Cuáles serán tus principales desafíos?  Planificar y ejecutar la actualización de las categorías asignadas de acuerdo con el calendario comercial.   Diseñar, revisar e implementar planogramas en salas de venta, asegurando su correcta ejecución.   Elaborar reportes y análisis de indicadores relacionados con planogramación, comportamiento de categorías y tendencias de mercado.   Desarrollar planogramas para campañas comerciales y realizar seguimiento a su implementación en los puntos de venta.   Gestionar la carga de coberturas de planogramas en SAP y monitorear la disponibilidad de stock asociada a las exhibiciones.   ¿Qué buscamos?  Personas con orientación analítica y atención al detalle.   Capacidad para interpretar información y transformarla en decisiones comerciales.   Habilidades de planificación, organización y coordinación transversal.   Interés por el retail, la gestión de categorías y la optimización de espacios comerciales.  Requisitos:   Formación universitaria Ingeniería Comercial, Ingeniería Industrial, Ingeniería en Control de Gestión, Ingeniería en Ejecución, Ingeniería en Administración de Empresas.   Al menos 2 años de experiencia en planogramación (EXCLUYENTE)   Conocimiento Excel avanzado   Perfil proactivo, ordenado y con alto nivel de responsabilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Jóvenes, Trabajo on-line</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Santiago de Chile, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Part-time - Remoto</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/jovenes-trabajo-on-line-1118372883.html</t>
+        </is>
+      </c>
+      <c r="G398" t="n">
+        <v>0</v>
+      </c>
+      <c r="H398" t="inlineStr"/>
+      <c r="I398" t="n">
+        <v>0</v>
+      </c>
+      <c r="J398" t="n">
+        <v>1</v>
+      </c>
+      <c r="K398" t="n">
+        <v>0</v>
+      </c>
+      <c r="L398" t="n">
+        <v>0</v>
+      </c>
+      <c r="M398" t="n">
+        <v>1</v>
+      </c>
+      <c r="N398" t="n">
+        <v>0</v>
+      </c>
+      <c r="O398" t="n">
+        <v>0</v>
+      </c>
+      <c r="P398" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>JÓVENES PARA TRABAJO ONLINE / 11.500 DIARIOSSi eres joven, estudiante o estás sin empleo, esta es tu oportunidad. Buscamos personas para ventas digitales con horarios flexibles.Ofrecemos:  Ganancias entre $11.500 y $23.000 diarios (3 a 6 hrs).  Bono de producción de $35.400 el primer día y $320.000 el segundo mes.  Trabajo independiente con desarrollo en redes sociales.Postula hoy y asegura tu cupo para la reunión virtual informativa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>MUJERES TODA EDAD PARA PROMOCIÓN Y VENTAS</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Santiago de Chile, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Part-time - Remoto</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/mujeres-toda-edad-para-promocion-y-ventas-1118372882.html</t>
+        </is>
+      </c>
+      <c r="G399" t="n">
+        <v>0</v>
+      </c>
+      <c r="H399" t="inlineStr"/>
+      <c r="I399" t="n">
+        <v>0</v>
+      </c>
+      <c r="J399" t="n">
+        <v>1</v>
+      </c>
+      <c r="K399" t="n">
+        <v>0</v>
+      </c>
+      <c r="L399" t="n">
+        <v>0</v>
+      </c>
+      <c r="M399" t="n">
+        <v>1</v>
+      </c>
+      <c r="N399" t="n">
+        <v>0</v>
+      </c>
+      <c r="O399" t="n">
+        <v>0</v>
+      </c>
+      <c r="P399" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>Importante empresa chilena del rubro alimenticio Busca  mujeres (chilenas o extranjeras) con o sin experiencia en el área de VentasCondiciones:  Horarios adaptables a tu disponibilidad.  Ganancias diarias desde el primer día.  Trabajo remoto desde tu celular.  Aplicación móvil personal para gestión de ventas.Postulando recibirás el detalle completo y acceso a la reunión virtual con la encargada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>OPORTUNIDAD PARA CESANTES- 1.158.000</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Rancagua, Región VI</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Full-time - Remoto</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/oportunidad-para-cesantes-1-158-000-1118372867.html</t>
+        </is>
+      </c>
+      <c r="G400" t="n">
+        <v>0</v>
+      </c>
+      <c r="H400" t="inlineStr"/>
+      <c r="I400" t="n">
+        <v>0</v>
+      </c>
+      <c r="J400" t="n">
+        <v>1</v>
+      </c>
+      <c r="K400" t="n">
+        <v>0</v>
+      </c>
+      <c r="L400" t="n">
+        <v>0</v>
+      </c>
+      <c r="M400" t="n">
+        <v>0</v>
+      </c>
+      <c r="N400" t="n">
+        <v>0</v>
+      </c>
+      <c r="O400" t="n">
+        <v>0</v>
+      </c>
+      <c r="P400" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>OPORTUNIDAD PARA CESANTES / $1.158.000 A MÁS FULL TIMEEmpresa nacional requiere hombres y mujeres mayores de 18 años, chilenos o extranjeros, con o sin experiencia en ventas.Ofrecemos:  Horarios flexibles.  Ingresos diarios y pagos quincenales.  Capacitación digital gratuita.  Trabajo remoto desde cualquier ciudad del país.Postula hoy mismo y obtén los detalles en una reunión virtual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>URGENTE TRABAJO A MEDIO TIEMPO</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Santiago de Chile, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Part-time - Remoto</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/urgente-trabajo-a-medio-tiempo-1118372866.html</t>
+        </is>
+      </c>
+      <c r="G401" t="n">
+        <v>0</v>
+      </c>
+      <c r="H401" t="inlineStr"/>
+      <c r="I401" t="n">
+        <v>0</v>
+      </c>
+      <c r="J401" t="n">
+        <v>1</v>
+      </c>
+      <c r="K401" t="n">
+        <v>0</v>
+      </c>
+      <c r="L401" t="n">
+        <v>0</v>
+      </c>
+      <c r="M401" t="n">
+        <v>1</v>
+      </c>
+      <c r="N401" t="n">
+        <v>0</v>
+      </c>
+      <c r="O401" t="n">
+        <v>0</v>
+      </c>
+      <c r="P401" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>TRABAJO ONLINE URGENTE / MEDIO TIEMPOEmpresa líder en América Latina busca con urgencia promotores y asesores de ventas para trabajar de manera remota desde cualquier zona de Chile.Requisitos: Manejo básico de redes sociales (Facebook e Instagram). Capacidad de organización y gestión de pedidos. Ser mayor de 18 años. Disponibilidad mínima de 3 horas diarias.Ofrecemos:  Ingresos mensuales entre $448.000 y $506.000 (part-time).  Bono de bienvenida + incentivos por metas cumplidas.  Trabajo remoto y estable todo el año.  Oportunidad de crecimiento dentro del equipo Multidesarrollo.Postula ahora y recibe información detallada del proyecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Práctica Diseño Gráfico - Diseño Digital</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>LimChile S.A</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Santiago de Chile, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/practica-diseno-grafico-diseno-digital-1118372862.html</t>
+        </is>
+      </c>
+      <c r="G402" t="n">
+        <v>0</v>
+      </c>
+      <c r="H402" t="inlineStr"/>
+      <c r="I402" t="n">
+        <v>0</v>
+      </c>
+      <c r="J402" t="n">
+        <v>0</v>
+      </c>
+      <c r="K402" t="n">
+        <v>0</v>
+      </c>
+      <c r="L402" t="n">
+        <v>1</v>
+      </c>
+      <c r="M402" t="n">
+        <v>0</v>
+      </c>
+      <c r="N402" t="n">
+        <v>1</v>
+      </c>
+      <c r="O402" t="n">
+        <v>0</v>
+      </c>
+      <c r="P402" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>Únete a LIMCHILE S.A., una empresa con más de 44 años de trayectoria en la gestión de personas y servicios integrales en todo Chile. Somos líderes en la industria, comprometidos con la innovación y la excelencia, y buscamos un practicante para el área de Comunicaciones que quiera desarrollarse profesionalmente en un entorno dinámico y desafiante. ¿Qué harás en este rol?  Apoyar en el desarrollo de piezas gráficas institucionales, contenidos para redes sociales, mailing, presentaciones, comunicados internos y material visual para campañas corporativas.  Manejo de herramientas de diseño como Illustrator, Photoshop, Canva, InDesign o similares. ¿Qué esperamos de ti?  Estudiante de carrera Diseño Gráfico, Diseño Digital, Comunicación Visual o carrera afín, con ganas de aprender y crecer en el área.  Conocimientos básicos de diseño para redes sociales y piezas digitales.  Deseable conocimiento en edición básica de video o motion graphics.  Contar con seguro escolar vigente para tu práctica profesional.  Mínimo 400 horas.  Proactividad, responsabilidad y trabajo en equipo. Condiciones de la práctica:  Jornada de lunes y martes de 8:30 a 18:00 horas, miércoles, jueves y viernes de 8:30 a 17:00 horas, que te permitirá organizar tu tiempo y compromisos. Beneficios que ofrecemos:  Incentivo económico mensual.  Oportunidad de integrarte a una empresa consolidada y reconocida en su rubro.  Ambiente de trabajo colaborativo donde podrás desarrollar habilidades esenciales para tu futuro profesional. Si buscas una práctica significativa, donde puedas aplicar tus conocimientos, crecer y formar parte de un equipo comprometido con la calidad y el servicio, LIMCHILE S.A. es el lugar ideal para ti. Postula y comienza tu camino hacia el éxito profesional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>ASESOR DE VENTAS EN NUTRICION Y MAQUILLAJE</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Cerro Navia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Full-time - Remoto</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/asesor-de-ventas-en-nutricion-y-maquillaje-1118372836.html</t>
+        </is>
+      </c>
+      <c r="G403" t="n">
+        <v>0</v>
+      </c>
+      <c r="H403" t="inlineStr"/>
+      <c r="I403" t="n">
+        <v>0</v>
+      </c>
+      <c r="J403" t="n">
+        <v>1</v>
+      </c>
+      <c r="K403" t="n">
+        <v>0</v>
+      </c>
+      <c r="L403" t="n">
+        <v>0</v>
+      </c>
+      <c r="M403" t="n">
+        <v>0</v>
+      </c>
+      <c r="N403" t="n">
+        <v>0</v>
+      </c>
+      <c r="O403" t="n">
+        <v>0</v>
+      </c>
+      <c r="P403" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>Estás buscando una oportunidad real para generar ingresos desde tu celular o computador, con horarios flexibles y acompañamiento constante? ¡Esta puede ser tu oportunidad!Buscamos personas proactivas, con ganas de aprender y mejorar su economía, para integrarse a un equipo en expansión dentro del área de bienestar, belleza y nutrición.No necesitas experiencia previa, ya que recibirás capacitación continua y trabajarás junto a personas con amplia trayectoria que te guiarán paso a paso.💸 Ofrecemos: Posibilidad de ganar entre $20.000 y $50.000 diarios según tu dedicación y resultados. Capacitación y acompañamiento personalizados. Horarios 100% flexibles. Oportunidad de crecimiento personal y profesional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>ejecutivo de ventas</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Conchalí, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Full-time - Remoto</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/ejecutivo-de-ventas-1118372829.html</t>
+        </is>
+      </c>
+      <c r="G404" t="n">
+        <v>0</v>
+      </c>
+      <c r="H404" t="inlineStr"/>
+      <c r="I404" t="n">
+        <v>0</v>
+      </c>
+      <c r="J404" t="n">
+        <v>1</v>
+      </c>
+      <c r="K404" t="n">
+        <v>0</v>
+      </c>
+      <c r="L404" t="n">
+        <v>1</v>
+      </c>
+      <c r="M404" t="n">
+        <v>0</v>
+      </c>
+      <c r="N404" t="n">
+        <v>0</v>
+      </c>
+      <c r="O404" t="n">
+        <v>0</v>
+      </c>
+      <c r="P404" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>Importante marca internacional en expansión busca incorporar personas motivadas para el desarrollo del canal comercial mediante la modalidad de distribución independiente y venta por comisión.​Funciones Principales:​Prospección y asesoría a clientes finales sobre nuestra línea de productos. ​Gestión de ventas a través de canales digitales y/o presenciales.​Construcción y liderazgo de equipos comerciales (opcional). ​Ofrecemos: ​Margen de ganancia inmediato por producto colocado + comisiones por volumen de equipo. ​Flexibilidad horaria para trabajar desde casa o terreno. ​Plan de incentivos, bonos en efectivo y viajes por cumplimiento de metas.​Requisitos: Residir en Chile, ser mayor de edad y contar con motivación para emprender. Postula y mantente atento a tu correo para coordinar tu asistencia a nuestra junta informativa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Analista de Notas de Crédito</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Pudahuel, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/analista-de-notas-de-credito-1118372824.html</t>
+        </is>
+      </c>
+      <c r="G405" t="n">
+        <v>3</v>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>analisis, excel</t>
+        </is>
+      </c>
+      <c r="I405" t="n">
+        <v>0</v>
+      </c>
+      <c r="J405" t="n">
+        <v>0</v>
+      </c>
+      <c r="K405" t="n">
+        <v>0</v>
+      </c>
+      <c r="L405" t="n">
+        <v>1</v>
+      </c>
+      <c r="M405" t="n">
+        <v>0</v>
+      </c>
+      <c r="N405" t="n">
+        <v>0</v>
+      </c>
+      <c r="O405" t="n">
+        <v>0</v>
+      </c>
+      <c r="P405" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>Importante Empresa del rubro Automotriz, busca "Analista de Notas de Crédito" para nuestro Centro de Distribución Ubicado en la comuna de Pudahuel.Horario de Trabajo es de Lunes a Viernes. (Horario Fijo), y se ofrece Contrato a Plazo Fijo renovable según desempeño.Requisitos: Titulo Técnico o Profesional en Contabilidad, Administración, Administración de Empresas, Finanzas o carrera Afín. Experiencia Minima de 1 a 3 años en áreas de facturación, cobranzas, créditos o contabilidad Conocimientos Técnicos: Manejo de Microsoft Excel a nivel Intermedio / Avanzado. Habilidades Clave: Alta capacidad de análisis, atención al detalle, resolución de problemas y excelentes habilidades de comunicación para tratar con clientesBeneficios: Bus de Acercamiento Casino Empresa Ropa de Trabajo Medio día por Cumpleaños Estacionamiento Aguinaldos Regalos, eventos y muchos beneficios más.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>CHILENAS O EXTRANJERAS - VENTAS PART TIME</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Arica, Región XV</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Part-time - Remoto</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/chilenas-o-extranjeras-ventas-part-time-1118372812.html</t>
+        </is>
+      </c>
+      <c r="G406" t="n">
+        <v>0</v>
+      </c>
+      <c r="H406" t="inlineStr"/>
+      <c r="I406" t="n">
+        <v>0</v>
+      </c>
+      <c r="J406" t="n">
+        <v>1</v>
+      </c>
+      <c r="K406" t="n">
+        <v>0</v>
+      </c>
+      <c r="L406" t="n">
+        <v>0</v>
+      </c>
+      <c r="M406" t="n">
+        <v>1</v>
+      </c>
+      <c r="N406" t="n">
+        <v>0</v>
+      </c>
+      <c r="O406" t="n">
+        <v>0</v>
+      </c>
+      <c r="P406" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>URGENTE : Mujeres para VENTAS PART TIME Chilenas o ExtranjerasTeletrabajo con o sin experiencia ; Genera $126.500 semanales part-time, con libre horarioOfrecemos :Horarios flexibles ,Ingresos todos los dias,Pagos QuincenalesEl trabajo consiste principalmente en Ventas y Supervicion de EquiposContaras con herramientas digitales para realizar el trabajo de forma remota en cualquier lugar de ChilePostula hoy , dejando tu correo electronico activo ; ahi recibirás la informacion detallada y horario de primera reunion Virtual para que puedas comenzar de manera inmediata</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Reemplazo Coordinador(a) de Ventas - Las Condes</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Las Condes, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/reemplazo-coordinador-a-de-ventas-las-condes-1118372811.html</t>
+        </is>
+      </c>
+      <c r="G407" t="n">
+        <v>0</v>
+      </c>
+      <c r="H407" t="inlineStr"/>
+      <c r="I407" t="n">
+        <v>0</v>
+      </c>
+      <c r="J407" t="n">
+        <v>0</v>
+      </c>
+      <c r="K407" t="n">
+        <v>0</v>
+      </c>
+      <c r="L407" t="n">
+        <v>1</v>
+      </c>
+      <c r="M407" t="n">
+        <v>0</v>
+      </c>
+      <c r="N407" t="n">
+        <v>0</v>
+      </c>
+      <c r="O407" t="n">
+        <v>0</v>
+      </c>
+      <c r="P407" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>Importante Institución de Educación Superior, se encuentra en búsqueda de un Coordinador(a) de Ventas para un reemplazo, quien tendrá como misión gestionar la operación comercial, ejecutando las ventas consultivas con la finalidad de asegurar el cumplimiento de los objetivos de captación y matrícula, en concordancia con los lineamientos estratégicos e institucionales. Principales Funciones: Gestionar el proceso de admisión de postulantes mediante un enfoque de venta consultiva, identificando sus necesidades e intereses.  Realizar el seguimiento oportuno y sistemático de los prospectos, utilizando los distintos canales de contacto.  Cumplir las metas de matrícula establecidas para los programas académicos bajo su responsabilidad, contribuyendo al logro de los objetivos comerciales e institucionales. Gestionar el pipeline de postulantes en el CRM institucional. Participar en ferias, eventos académicos y actividades de difusión.  Asegurar una experiencia de atención consistente y de alta calidad durante todo el proceso de admisión. Requisitos para postular:  Título profesional en área tales como Administración de Empresas, Comunicaciones, Relaciones Públicas o carreras similares.  Contar con especialización en ventas, experiencia de clientes o servicios.  Al menos 2 años de experiencia en admisión ventas en instituciones de educación superior y manejo de CRM. Esta oferta se enmarca en la Ley N° 21.015, que promueve la inclusión laboral de personas con discapacidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>TRABAJA ONLINE, EN CUALQUIER REGIÓN</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Santiago de Chile, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Part-time - Remoto</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/trabaja-online-en-cualquier-region-1118372810.html</t>
+        </is>
+      </c>
+      <c r="G408" t="n">
+        <v>0</v>
+      </c>
+      <c r="H408" t="inlineStr"/>
+      <c r="I408" t="n">
+        <v>0</v>
+      </c>
+      <c r="J408" t="n">
+        <v>1</v>
+      </c>
+      <c r="K408" t="n">
+        <v>0</v>
+      </c>
+      <c r="L408" t="n">
+        <v>1</v>
+      </c>
+      <c r="M408" t="n">
+        <v>1</v>
+      </c>
+      <c r="N408" t="n">
+        <v>0</v>
+      </c>
+      <c r="O408" t="n">
+        <v>0</v>
+      </c>
+      <c r="P408" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>TRABAJA ON-LINE / DESDE CUALQUIER REGIÓN DE CHILEDebido a la gran demanda de nuestros productos buscamos personas sin experiencia en ventas para incorpórarse a nuestro equipo , genera entre $448.000 a $506.000 mensuales, trabajando por internet desde cualquier lugar de Chile (Part-time)Contaras con todo el apoyo de nuestro equipo de trabajo mas la guia de un tutor que te acompañara en tu aprendizaje.Con o sin experiencia, ya que contamos con entrenamientos virtuales desde el primer momentoPodrás comenzar a ganar dinero desde el primer dia aprovechando las herramientas digitales que te facilitaremos, tales como:  Pagina web (gratis)  Aplicacion movil (opcional)  Cursos en linea y presencial  Sistema automatizado de ventas webPostula hoy y accede a Reunión virtualENVIAREMOS INFORMACION DETALLADA AL CORREO , DE ACUERDO A SU POSTULACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Enfermero(a) Administrativo(a) Asistencial - La Florida</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>La Florida, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/enfermero-a-administrativo-a-asistencial-la-florida-1118372805.html</t>
+        </is>
+      </c>
+      <c r="G409" t="n">
+        <v>0</v>
+      </c>
+      <c r="H409" t="inlineStr"/>
+      <c r="I409" t="n">
+        <v>0</v>
+      </c>
+      <c r="J409" t="n">
+        <v>0</v>
+      </c>
+      <c r="K409" t="n">
+        <v>0</v>
+      </c>
+      <c r="L409" t="n">
+        <v>1</v>
+      </c>
+      <c r="M409" t="n">
+        <v>0</v>
+      </c>
+      <c r="N409" t="n">
+        <v>0</v>
+      </c>
+      <c r="O409" t="n">
+        <v>0</v>
+      </c>
+      <c r="P409" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>Importante Clínica se encuentra en búsqueda de Enfermero(a) Administrativo (a) Asistencial, quien tendrá como misión velar por el cumplimiento de los estándares de calidad, seguridad del paciente y normativa sanitaria de la Clínica, promoviendo la mejora continua de los procesos clínicos y administrativos mediante la implementación, supervisión y evaluación de protocolos, indicadores y estrategias que contribuyan a una atención segura, eficiente y de excelencia. Principales Funciones:  Asegurar el cumplimiento de los protocolos clínicos, procedimientos de bioseguridad, esterilización y normativa sanitaria vigente. Diseñar, implementar y monitorear el sistema de gestión de calidad, elaborando protocolos, indicadores y planes de mejora continua. Coordinar acciones orientadas a la calidad y seguridad del paciente.  Supervisar y coordinar el funcionamiento de las unidades clínicas y del personal clínico y clínico-administrativo. Desarrollar e impartir programas de capacitación e inducción en protocolos clínicos, bioseguridad y otras materias relacionadas con la calidad y seguridad de la atención. Requisitos para postular: Título profesional de Enfermera(o) con Diplomado en IAAS. Al menos 1 año de experiencia en el área clínica y administrativa. Tener cursos de acreditación o gestión de calidad en salud. Esta oferta se enmarca en la Ley N° 21.015, que promueve la inclusión laboral de personas con discapacidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Bodeguero-a – Sucursal DTSA Santiago</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Komatsu Cummins</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Quilicura, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/bodeguero-a-sucursal-dtsa-santiago-1118372802.html</t>
+        </is>
+      </c>
+      <c r="G410" t="n">
+        <v>0</v>
+      </c>
+      <c r="H410" t="inlineStr"/>
+      <c r="I410" t="n">
+        <v>0</v>
+      </c>
+      <c r="J410" t="n">
+        <v>0</v>
+      </c>
+      <c r="K410" t="n">
+        <v>0</v>
+      </c>
+      <c r="L410" t="n">
+        <v>1</v>
+      </c>
+      <c r="M410" t="n">
+        <v>0</v>
+      </c>
+      <c r="N410" t="n">
+        <v>0</v>
+      </c>
+      <c r="O410" t="n">
+        <v>0</v>
+      </c>
+      <c r="P410" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>El Grupo Komatsu Cummins es una empresa inclusiva, comprometida con la promoción de la diversidad, la equidad y la igualdad de oportunidades. Incorporamos al mercado experiencia, tecnología, soporte e innovación, consolidándonos como uno de los líderes mundiales en nuestro rubro.Propósito del cargoEjecutar y controlar las operaciones de recepción, almacenamiento, inventario y despacho de materiales, asegurando la trazabilidad, el orden y la disponibilidad oportuna de los productos, de acuerdo con los procedimientos internos y las normas de seguridad vigentes.Principales funciones Recepcionar, revisar y almacenar materiales de acuerdo con los procedimientos establecidos.Preparar y despachar materiales según los requerimientos operacionales.Mantener el orden, la limpieza y la correcta identificación de los materiales en bodega.Registrar y controlar inventarios físicos y sistémicos.Apoyar en inventarios periódicos y conteos cíclicos.Cumplir con las normas de seguridad, higiene, orden y medio ambiente.Coordinar con las distintas áreas internas para asegurar la continuidad del suministro. Requisitos Mínimos: Requisitos Enseñanza Media Completa.Deseable experiencia en operaciones de bodega, logística o cargos similares.Deseable conocimiento en control de inventarios y manejo de sistemas de bodega.Disponibilidad para desempeñarse en la sucursal DTSA Santiago. Importante: Adjunta tu currículum actualizado al momento de postular. Esta oferta se rige bajo la Ley N.° 21.015, que incentiva la inclusión de personas con discapacidad al mundo laboral. En Komatsu Cummins buscamos a los mejores talentos para incorporarse a nuestra compañía, independiente de su género, orientación sexual, situación de discapacidad, nacionalidad, edad, cultura u origen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Administrativo-a de Compras Sucursal Lo Boza</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Komatsu Cummins</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Pudahuel, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/administrativo-a-de-compras-sucursal-lo-boza-1118372799.html</t>
+        </is>
+      </c>
+      <c r="G411" t="n">
+        <v>1</v>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I411" t="n">
+        <v>0</v>
+      </c>
+      <c r="J411" t="n">
+        <v>0</v>
+      </c>
+      <c r="K411" t="n">
+        <v>0</v>
+      </c>
+      <c r="L411" t="n">
+        <v>1</v>
+      </c>
+      <c r="M411" t="n">
+        <v>0</v>
+      </c>
+      <c r="N411" t="n">
+        <v>0</v>
+      </c>
+      <c r="O411" t="n">
+        <v>0</v>
+      </c>
+      <c r="P411" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>El grupo Komatsu Cummins es una empresa inclusiva, comprometida con la promoción de la diversidad, equidad e igualdad de oportunidades. Nuestra empresa incorpora al mercado experiencia, tecnología, soporte e innovación siendo uno de los líderes mundiales en su rubro. Cargo: Administrativo/a de Compras Sucursal Lo Boza  Propósito del Cargo:Apoyar la gestión del proceso de compras nacionales de bienes y servicios de tipo estándar o de baja complejidad mediante la ejecución de tareas administrativas, control documental(sistema ERP),y coordinación con proveedores, asegurando el cumplimiento de los procedimientos internos y la disponibilidad oportuna de insumos y materiales con el fin de asegurar con eficiencia la continuidad operativa de las distintas áreas de la Compañía, con una foco en la sustentabilidad.  Funciones y Responsabilidades: órdenes de compra en el sistema ERP y mantener actualizado el archivo digital para tener la trazabilidad del proceso y el documento formal de compras.Hacer seguimiento a las órdenes de compra y confirmar fechas de entrega con proveedores para tener controlado el proceso.Solicitar cotizaciones y recopilar información para análisis comparativo y oportunidades de ahorro.Coordinar con áreas usuarias para validar requerimientos y apoyar en reportes de compras y KPI del área para coordinar y mantener una relación cooperativa con el Comprador Nacional, cliente interno y proveedor.Monitorear KPIs del área de compras para asegurar su eficiencia y cumplimiento de metas. Requisitos Mínimos: Requisitos:Residencia en la region metropolitana.Microsoft office Intermedio o básicaConocimiento Sistema SAP deseableTitulado en tecnico medio y/o superior con especialidad en Administración de empresas, , logística, Comercio Exterior.al menos 1 año de experiencia, idealmente en compras o logística.Esta oferta se rige bajo la Ley N°21.015, que incentiva la inclusión de personas con discapacidad al mundo laboral. Buscamos a los mejores talentos para incorporarse a nuestra compañía independiente del género, orientación sexual, situación de discapacidad, nacionalidad, edad, cultura y origen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Mujeres para trabajo Remoto, 448.000 media jornada</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Santiago de Chile, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Part-time - Remoto</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/mujeres-para-trabajo-remoto-448-000-media-jornada-1118372764.html</t>
+        </is>
+      </c>
+      <c r="G412" t="n">
+        <v>0</v>
+      </c>
+      <c r="H412" t="inlineStr"/>
+      <c r="I412" t="n">
+        <v>0</v>
+      </c>
+      <c r="J412" t="n">
+        <v>1</v>
+      </c>
+      <c r="K412" t="n">
+        <v>0</v>
+      </c>
+      <c r="L412" t="n">
+        <v>1</v>
+      </c>
+      <c r="M412" t="n">
+        <v>1</v>
+      </c>
+      <c r="N412" t="n">
+        <v>0</v>
+      </c>
+      <c r="O412" t="n">
+        <v>0</v>
+      </c>
+      <c r="P412" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>MUJERES PARA TRABAJO REMOTO / 448.000 (media jornada)Estamos buscando de manera URGENTE a personas que necesiten trabajar con libertad de horario de manera inmediata.OFRECEMOS :INGRESOS DESDE EL PRIMER DIA POR VENTAS Y TAMBIEN UN BONO EL PRIMER DIA POR METASTENDRAS HERRAMIENTAS DIGITALES INMEDIATAS PARA QUE PUEDAS DESARROLLARTE DE MANERA INTEGRAL  PAGINA WEB PERSONAL CON CARRITO DE VENTA INTERNACIONAL  APLICACION MOVIL PARA LLEVAR EN LA PALMA DE TU MANO TODAS LAS VENTAS  CURSOS EN LINEA Y PRESENCIAL  SISTEMA AUTOMATIZADO DE ENVIOS A TODO EL PAIS CON CONVENIO CON LAS MEJORES EMPRESASPuedes o no tener experiencia en el área , ya que desde el primer día contaras con ENTRENAMIENTO PERSONALIZADOPOSTULA HOY Y ACCEDE A REUNION VIRTUALENVIAREMOS INFORMACION DETALLADA AL CORREO</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>PROFESORES EDUCACIÓN FÍSICA- TRES HORAS DIA</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Santiago de Chile, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Por Horas - Híbrido</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/profesores-educacion-fisica-tres-horas-dia-1118372762.html</t>
+        </is>
+      </c>
+      <c r="G413" t="n">
+        <v>0</v>
+      </c>
+      <c r="H413" t="inlineStr"/>
+      <c r="I413" t="n">
+        <v>0</v>
+      </c>
+      <c r="J413" t="n">
+        <v>0</v>
+      </c>
+      <c r="K413" t="n">
+        <v>1</v>
+      </c>
+      <c r="L413" t="n">
+        <v>0</v>
+      </c>
+      <c r="M413" t="n">
+        <v>1</v>
+      </c>
+      <c r="N413" t="n">
+        <v>0</v>
+      </c>
+      <c r="O413" t="n">
+        <v>0</v>
+      </c>
+      <c r="P413" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>ATENCION PROFESORES DE EDUCACIÓN FÍSICA !!Buscamos Profesores de Educación física o Preparadores fisicos de cualquier edad para trabajar en Ventas dedicando desde 3 horas al dia, $506.280 mensuales (1 producto diario)Las ventas se realizan a traves de Pagina web y contamos con envios gratuitos a todo el pais .Recibiras:  Sitio web personalizado  App Movil  Call center gratuito para ti y tus clientes con especialistas  Entrenamientos virtuales semanales constantes  Bono el primer dia y ademas mensuales en dinero*Tenemos formato PART-TIME especial para profesores o personas que necesitan un segundo ingreso o trabajar desde su casa.Postula ahora y te citaremos a una reunion en a la brevedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>290.000 SEMANALES- REMOTO</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Concepción, Región VIII</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Full-time - Remoto</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/290-000-semanales-remoto-1118372750.html</t>
+        </is>
+      </c>
+      <c r="G414" t="n">
+        <v>0</v>
+      </c>
+      <c r="H414" t="inlineStr"/>
+      <c r="I414" t="n">
+        <v>0</v>
+      </c>
+      <c r="J414" t="n">
+        <v>1</v>
+      </c>
+      <c r="K414" t="n">
+        <v>0</v>
+      </c>
+      <c r="L414" t="n">
+        <v>0</v>
+      </c>
+      <c r="M414" t="n">
+        <v>1</v>
+      </c>
+      <c r="N414" t="n">
+        <v>0</v>
+      </c>
+      <c r="O414" t="n">
+        <v>0</v>
+      </c>
+      <c r="P414" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>Buscamos personas de cualquier edad / 290.000 semanalesTRABAJO DE VENTAS con modalidad REMOTO (horarios flexibles)Las ventas se realizan a traves de Pagina web y contamos con envios gratuitos a todo el pais .Recibiras:Sitio web personal. (Gratis)App Movil (opcional)Call center gratuito para ti y tus clientesEntrenamientos virtuales semanales constantesBono el primer día y ademas mensuales en dinero*Tenemos ademas formato PART-TIME especial para estudiantes o personas que necesitan un segundo ingreso o trabajar desde su casa.Postula ahora y accede a la informacion detallada y reunión virtual</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>EN TODAS LAS REGIONES PARA EQUIPO DE LATAM</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Santiago de Chile, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Full-time - Remoto</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/en-todas-las-regiones-para-equipo-de-latam-1118372749.html</t>
+        </is>
+      </c>
+      <c r="G415" t="n">
+        <v>0</v>
+      </c>
+      <c r="H415" t="inlineStr"/>
+      <c r="I415" t="n">
+        <v>0</v>
+      </c>
+      <c r="J415" t="n">
+        <v>1</v>
+      </c>
+      <c r="K415" t="n">
+        <v>0</v>
+      </c>
+      <c r="L415" t="n">
+        <v>1</v>
+      </c>
+      <c r="M415" t="n">
+        <v>0</v>
+      </c>
+      <c r="N415" t="n">
+        <v>0</v>
+      </c>
+      <c r="O415" t="n">
+        <v>0</v>
+      </c>
+      <c r="P415" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>Con urgencia necesitamos vendedores por internet hacia todas las regiones !!!Incorpórate a nuestro equipo de vendedores y genera sobre $1.158.000 mensual con libertad absoluta de horariosContaras con todo el apoyo de nuestro equipo de trabajo mas la guia de un tutor que te acompañara en tu aprendizaje.Con o sin experiencia.Comenzaras a ganar dinero desde el primer dia aprovechando las herramientas digitales que te facilitaremos, tales como:  Pagina web  Aplicacion movil  Cursos en linea y presencial  Sistema automatizado de ventas webPostula hoy y accede a nuestra sala virtual"cupos limitados para cada region"</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Ayudante de Gerente de Restaurant</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Talca, Región VII</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/ayudante-de-gerente-de-restaurant-1118372631.html</t>
+        </is>
+      </c>
+      <c r="G416" t="n">
+        <v>0</v>
+      </c>
+      <c r="H416" t="inlineStr"/>
+      <c r="I416" t="n">
+        <v>0</v>
+      </c>
+      <c r="J416" t="n">
+        <v>0</v>
+      </c>
+      <c r="K416" t="n">
+        <v>0</v>
+      </c>
+      <c r="L416" t="n">
+        <v>1</v>
+      </c>
+      <c r="M416" t="n">
+        <v>0</v>
+      </c>
+      <c r="N416" t="n">
+        <v>0</v>
+      </c>
+      <c r="O416" t="n">
+        <v>0</v>
+      </c>
+      <c r="P416" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>Resumen del PuestoBuscamos un Ayudante de Gerente de Restaurant con experiencia para supervisar y optimizar todas las facetas de la operación de un restaurante. El candidato ideal será un líder proactivo, enfocado en la excelencia del servicio al cliente y la eficiencia operativa.Responsabilidades Gestionar y administrar la operación general del restaurante, asegurando el cumplimiento de los estándares de servicio. Supervisar el control de costos, inventario y gastos. Monitorear y gestionar Indicadores Clave de Desempeño (KPIs). Administrar los horarios y tareas del personal. Asegurar el cumplimiento de los objetivos de auditoría de calidad interna y evaluaciones de cliente incógnito. Impulsar el desarrollo de las ventas y la experiencia del cliente. Controlar los tiempos y la eficiencia de las operaciones de cocina. Proponer e implementar mejoras para optimizar el funcionamiento del restaurante. Garantizar el cumplimiento de las normativas sanitarias y de inocuidad alimentaria. Supervisar el uso de recursos financieros, equipamiento, infraestructura y personal, informando sobre cualquier desviación. Controlar mermas, pérdidas y desviaciones de stock.Requisitos Experiencia comprobada de 3 años en gestión de operaciones de restaurantes. Sólidos conocimientos en control de costos, inventario y gestión financiera. Capacidad demostrada para liderar y motivar equipos. Excelentes habilidades de resolución de problemas y toma de decisiones. Conocimiento de normativas sanitarias y de seguridad alimentaria. Orientación a resultados y al servicio al cliente. Habilidades de comunicación efectiva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Cajero-a Turnos Rotativos - Guacamole Parque Arauco</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Niu Foods</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Las Condes, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/cajero-a-turnos-rotativos-guacamole-parque-arauco-1118368968.html</t>
+        </is>
+      </c>
+      <c r="G417" t="n">
+        <v>0</v>
+      </c>
+      <c r="H417" t="inlineStr"/>
+      <c r="I417" t="n">
+        <v>0</v>
+      </c>
+      <c r="J417" t="n">
+        <v>0</v>
+      </c>
+      <c r="K417" t="n">
+        <v>0</v>
+      </c>
+      <c r="L417" t="n">
+        <v>1</v>
+      </c>
+      <c r="M417" t="n">
+        <v>0</v>
+      </c>
+      <c r="N417" t="n">
+        <v>0</v>
+      </c>
+      <c r="O417" t="n">
+        <v>0</v>
+      </c>
+      <c r="P417" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>¡Guacamole sigue creciendo y llegamos a Mall Parque Arauco!Holding Niu Foods dedicado al rubro gastronómico, cuenta con una Marca empleadora única en experiencia y calidad en cuanto a productos frescos y ricos basados en comida Tex-Mex. Con más de 12 locales activos en Santiago y próximamente nuestro Nuevo local que se encontrara ubicado en Mall Parque Arauco.Es por esto que nos encontramos en búsqueda de una persona ordenada y responsable que cuente con experiencia en caja para desempeñarse en el cargo descrito.Requisitos: Experiencia en caja (comprobable con carta de recomendación o referencias laborales) EXCLUYENTE  Disponibilidad de trabajar en horario mall Documentación vigenteHorarios: Se trabajará con horarios rotativos de lunes a domingo (AM- INTERMEDIO - PM) Respetaremos tus días libres a la semana es por esto que tendremos semanas 6x1 y 5x2Renta: Renta base $553.000 + Bono de Asistencia $50.000+ Asignación de Caja $50.000+ Uniforme + AlmuerzoBeneficios: Desarrollo de carrera interna (Programa de formación de Líderes) Convenios Oncológicos, dentales, Gimnasios, Salud Mental Gif card de cumpleaños, Aguinaldos Septiembre y Diciembre Seguro de Accidentes Ingreso a caja de compensación Los Andes y a la ACHS 20% de descuento en todas nuestras marcas¡Postula y forma parte de esta gran familia!</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>SUBGERENTE DE LOCAL HOLDING NIU FOODS- RUBRO GASTRONÓMICO SANTIAGO</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Niu Foods</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Santiago de Chile, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/subgerente-de-local-holding-niu-foods-rubro-gastronomico-santiago-1118317865.html</t>
+        </is>
+      </c>
+      <c r="G418" t="n">
+        <v>0</v>
+      </c>
+      <c r="H418" t="inlineStr"/>
+      <c r="I418" t="n">
+        <v>0</v>
+      </c>
+      <c r="J418" t="n">
+        <v>0</v>
+      </c>
+      <c r="K418" t="n">
+        <v>0</v>
+      </c>
+      <c r="L418" t="n">
+        <v>1</v>
+      </c>
+      <c r="M418" t="n">
+        <v>0</v>
+      </c>
+      <c r="N418" t="n">
+        <v>0</v>
+      </c>
+      <c r="O418" t="n">
+        <v>0</v>
+      </c>
+      <c r="P418" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>¡¡SE PARTE DE NUESTRO EQUIPO NIU SUSHI !!Importante Holding del Rubro Gastronómico está en búsqueda de Sub Gerentes para unirse a su prestigiosa cadena que cuenta actualmente con más de 60 locales a nivel Nacional e Internacional. Nuestas marcas Guacamole, Niu Sushi y Niu Express.Ofrecemos capacitación y pasantías internas, las cuales son obligatorias independiente de los conocimientos y experiencia que mantenga el candidato, con la finalidad de posicionarse con todas las herramientas necesarias para Liderar nuestros equipos de trabajo.Jornada laboral en formato de locales calle de lunes a sábado o en formato de locales en Mall de lunes a domingo, en Horario PM de 17:30hrs hasta el cierre de local. Se trabaja con ARTICULO 22.Sueldo Base por período de capacitación $600.000 + $200.000 de bono por periodo de capacitación + Bonos por cumplimiento de Metas una vez finalizado el proceso de capacitación.Ofrecemos estabilidad Laboral, Trabajo en Equipo, Oportunidad de perfeccionamiento y crecimiento interno, Un grato ambiente de trabajo y permanecer a una cadena líder en el mercado del Sushi.CUALIFICACIONES- Poseer un título técnico o profesional en áreas a fines.- Idealmente con 2 años de experiencia previa en el rubro gastronómico.- Disponibilidad de trabajo en el turno PM.- Disponibilidad para movilidad interna en locales Mall y calle.BENEFICIOS- Posibilidad de crecimiento y desarrollo interno.- 20% de descuentos en productos de la cadena (para colaboradores)- Convenios con gimnasio- Convenios Psicológicos- Convenios con Clínicas Odontológicas- Seguro de Accidentes ACHTE ESPERAMOS!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Administrador (Subgerente) de Local Guacamole Restaurant - HOLDING NIU FOODS</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Niu Foods</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Santiago De Chile, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/administrador-subgerente-de-local-guacamole-restaurant-holding-niu-foods-1118317836.html</t>
+        </is>
+      </c>
+      <c r="G419" t="n">
+        <v>0</v>
+      </c>
+      <c r="H419" t="inlineStr"/>
+      <c r="I419" t="n">
+        <v>0</v>
+      </c>
+      <c r="J419" t="n">
+        <v>0</v>
+      </c>
+      <c r="K419" t="n">
+        <v>0</v>
+      </c>
+      <c r="L419" t="n">
+        <v>1</v>
+      </c>
+      <c r="M419" t="n">
+        <v>0</v>
+      </c>
+      <c r="N419" t="n">
+        <v>0</v>
+      </c>
+      <c r="O419" t="n">
+        <v>0</v>
+      </c>
+      <c r="P419" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>¡¡SE PARTE DE NUESTRO EQUIPO NIU SUSHI !!GUACAMOLE, es una cadena de Restaurantes dedicados a la comida Tex Mex, marca en expansión y la cual se encuentra en un potente crecimiento.Esta marca perteneciente a nuestro Holding gastronomico NIU FOODS, donde tambien contamos con Marcas reconocidas como Niu Sushi, se encuentra en la busqueda de Sub Gerentes en entrenamiento para unirse a esta prestigiosa cadena que posee marcas importantes posicionadas y fidelizadas nacional e internacionalmente, con más de 60 locales (total entre todas sus marcas).Ofrecemos capacitación y pasantías internas, las cuales son obligatorias independiente de los conocimientos y experiencia que mantenga el candidato, con la finalidad de posicionarse con todas las herramientas necesarias para Liderar nuestros equipos de trabajo.Jornada laboral en formato de locales calle de lunes a sábado o en formato de locales en Mall de lunes a domingo, en Horario PM de 17:30 hrs hasta el cierre de local. Se trabaja con ARTICULO 22.Sueldo Base por período de capacitación $600.000 + $200.000 de bono por periodo de capacitación + Bonos por cumplimiento de Metas una vez finalizado el proceso de capacitación.Ofrecemos estabilidad Laboral, Trabajo en Equipo, Oportunidad de perfeccionamiento y crecimiento interno, Un grato ambiente de trabajo y permanecer a una cadena líder en el mercado del Sushi.CUALIFICACIONES- Poseer un título técnico o profesional en áreas a fines.- Idealmente con 2 años de experiencia previa en el rubro gastronómico.- Disponibilidad de trabajo en el turno PM.BENEFICIOS- Posibilidad de crecimiento y desarrollo interno.- Convenios con gimnasio- Convenios Psicológicos- Convenios con Clínicas Odontológicas- Seguro de Accidentes ACH- 20% de descuentos en compras en nuestras marcasTE ESPERAMOS!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Administrador de Local NIU EXPRESS - HOLDING GASTRONOMICO NIU FOODS</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Niu Foods</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Santiago de Chile, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/administrador-de-local-niu-express-holding-gastronomico-niu-foods-1118296377.html</t>
+        </is>
+      </c>
+      <c r="G420" t="n">
+        <v>0</v>
+      </c>
+      <c r="H420" t="inlineStr"/>
+      <c r="I420" t="n">
+        <v>0</v>
+      </c>
+      <c r="J420" t="n">
+        <v>0</v>
+      </c>
+      <c r="K420" t="n">
+        <v>0</v>
+      </c>
+      <c r="L420" t="n">
+        <v>1</v>
+      </c>
+      <c r="M420" t="n">
+        <v>0</v>
+      </c>
+      <c r="N420" t="n">
+        <v>0</v>
+      </c>
+      <c r="O420" t="n">
+        <v>0</v>
+      </c>
+      <c r="P420" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>¡¡SE PARTE DE NUESTRO EQUIPO NIU EXPRESS!!NIU EXPRESS, es una cadena de Restaurantes ubicado en los patios de comida de los mall, marca en expansión y la cual se encuentra en un potente crecimiento.Esta marca perteneciente a nuestro Holding gastronomico NIU FOODS, donde tambien contamos con Marcas reconocidas como Niu Sushi, se encuentra en la busqueda de Sub Gerentes en entrenamiento para unirse a esta prestigiosa cadena que posee marcas importantes posicionadas y fidelizadas nacional e internacionalmente, con más de 60 locales (total entre todas sus marcas).Ofrecemos capacitación y pasantías internas, las cuales son obligatorias independiente de los conocimientos y experiencia que mantenga el candidato, con la finalidad de posicionarse con todas las herramientas necesarias para Liderar nuestros equipos de trabajo.Jornada laboral en formato de locales calle de lunes a sábado o en formato de locales en Mall de lunes a domingo, en Horario PM de 17:30 hrs hasta el cierre de local. Se trabaja con ARTICULO 22.Sueldo Base por período de capacitación y un bono por periodo de capacitación + Bonos por cumplimiento de Metas una vez finalizado el proceso de capacitación.Ofrecemos estabilidad Laboral, Trabajo en Equipo, Oportunidad de perfeccionamiento y crecimiento interno, Un grato ambiente de trabajo y permanecer a una cadena líder en el mercado del Sushi.CUALIFICACIONES- Titulo técnico o profesional en áreas afines al rubro gastronómico, administración o servicio.- Experiencia mínima de 2 años en sector gastronómico (deseable)- Disponibilidad para trabajar en turnos Pm y en horarios rotativos, incluyendo fines de semana y festivos.- Experiencia en atención en centros comerciales o alto flujo de publico (deseable), con foco en resolución de conflictos y servicio al cliente.- Interés y potencial para asumir funciones de liderazgo.- Capacidad para desempeñarse en entornos dinámicos y de ritmo rápido.- Habilidades de comunicación efectiva y buenas relaciones interpersonales.- Actitud proactiva, orientación al aprendizaje y mejora continua.- Fuerte orientación al servicio y experiencia del cliente.- Capacidad de gestión eficiente y rapidez en la resolución de tareas.- Perfil resolutivo, autónomo y con iniciativa.BENEFICIOS- Posibilidad de crecimiento y desarrollo interno.- Convenios con gimnasio- Convenios Psicológicos- Convenios con Clínicas Odontológicas- Seguro de Accidentes ACHS- 20% de descuentos en compras en nuestras marcas¡Se parte de nososotros!</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Ejecutiva de Ventas Digitales por TikTok – Servicios de Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Lakes Solutions SpA</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Macul, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Full-time - Híbrido</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/ejecutiva-de-ventas-digitales-por-tiktok-servicios-de-telecomunicaciones-1118357175.html</t>
+        </is>
+      </c>
+      <c r="G421" t="n">
+        <v>0</v>
+      </c>
+      <c r="H421" t="inlineStr"/>
+      <c r="I421" t="n">
+        <v>0</v>
+      </c>
+      <c r="J421" t="n">
+        <v>0</v>
+      </c>
+      <c r="K421" t="n">
+        <v>1</v>
+      </c>
+      <c r="L421" t="n">
+        <v>1</v>
+      </c>
+      <c r="M421" t="n">
+        <v>0</v>
+      </c>
+      <c r="N421" t="n">
+        <v>0</v>
+      </c>
+      <c r="O421" t="n">
+        <v>0</v>
+      </c>
+      <c r="P421" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>El puesto consiste en realizar ventas digitales de portabilidades y servicios móviles de una empresa de telecomunicaciones a través de TikTok y redes sociales.Buscamos personas con actitud comercial, buena comunicación, seguridad frente a cámara, responsabilidad y ganas reales de vender. La persona seleccionada deberá promocionar los servicios, generar interacción con potenciales clientes, explicar beneficios de portabilidad y planes móviles, y apoyar la captación de interesados mediante contenido digital y conexión frente a cámara.Funciones principales: Promocionar y vender portabilidades y servicios móviles a través de TikTok. Presentar ofertas y beneficios de manera clara, dinámica y profesional. Conectarse frente a cámara para generar contenido, interacción y oportunidades de venta. Gestionar interesados y orientar a potenciales clientes durante el proceso comercial. Participar en capacitaciones sobre producto, ventas digitales y uso de plataformas. Mantener responsabilidad, puntualidad y compromiso con los horarios establecidos.Modalidad de trabajo:El trabajo es de modalidad híbrida, de lunes a viernes. 09:00 a 13:00 hrs presencial en oficina ubicada en Macul. 18:00 a 22:00 hrs conexión desde casa.La jornada de la tarde se realiza de forma remota, ya que corresponde al horario de mayor movimiento y visualización en TikTok.Requisitos: Actitud comercial y orientación a resultados. Buena comunicación y personalidad frente a cámara. Seguridad, dinamismo y disposición para vender. Manejo básico de redes sociales, especialmente TikTok. Experiencia en ventas, promociones, atención al cliente, retail o telecomunicaciones deseable, no excluyente. Responsabilidad, puntualidad y compromiso. Disposición para aprender ventas digitales y técnicas de comunicación por redes sociales.Proceso de selección:Primero se realiza una entrevista inicial con el cliente. Si la persona queda aprobada, pasa a una capacitación pagada de 2 días, donde se explica el producto, el proceso de venta y la forma de trabajo. Posterior a la capacitación, se formaliza el ingreso con contrato.Se ofrece: Sueldo base mensual de $650.000. Comisiones por venta. Bonos por responsabilidad, asistencia y puntualidad. Capacitación pagada. Contrato posterior a aprobación y capacitación. Posibilidad de generar ingresos superiores a $2.000.000 mensuales según desempeño y resultados comerciales.Es una oportunidad ideal para personas con personalidad, actitud positiva, habilidades comunicacionales y ganas de crecer en el área de ventas digitales.Para postular, se debe enviar la siguiente información: Nombre completo. Edad. Comuna de residencia. Experiencia laboral, si es que tiene experiencia en ventas, promociones, atención al cliente, redes sociales o telecomunicaciones. Disponibilidad para trabajar en la modalidad y horarios indicados. Fotos actuales de presentación laboral, idealmente una foto de rostro y una foto de medio cuerpo, con buena luz y presentación ordenada.Las fotos solicitadas son únicamente para armar el perfil de postulación y presentarlo al cliente, considerando que el trabajo requiere comunicación y presentación frente a cámara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Encargado Contable</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Carlos  Cereceda</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Providencia, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/encargado-contable-1118372841.html</t>
+        </is>
+      </c>
+      <c r="G422" t="n">
+        <v>2</v>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>power bi</t>
+        </is>
+      </c>
+      <c r="I422" t="n">
+        <v>0</v>
+      </c>
+      <c r="J422" t="n">
+        <v>0</v>
+      </c>
+      <c r="K422" t="n">
+        <v>0</v>
+      </c>
+      <c r="L422" t="n">
+        <v>1</v>
+      </c>
+      <c r="M422" t="n">
+        <v>0</v>
+      </c>
+      <c r="N422" t="n">
+        <v>0</v>
+      </c>
+      <c r="O422" t="n">
+        <v>0</v>
+      </c>
+      <c r="P422" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>Encargado Contable Resumen del Puesto Buscamos un profesional proactivo y con capacidad para proponer mejoras para unirse a nuestro equipo como Encargado Contable. El candidato ideal tendrá experiencia en la gestión de cartera de clientes y un sólido conocimiento de los procesos contables. Responsabilidades  Gestión de cartera de clientes. Confección de Balances, Estados de Resultados, Flujo de Caja y conciliaciones. Elaboración de informes, se valorará experiencia con Power BI. Manejo de sistemas ERP. Colaborar en la mejora continua de los procesos contables.  Requisitos  Título de Contador Auditor. Experiencia comprobable en puestos contables similares. Capacidad para trabajar de forma autónoma y proponer soluciones. Habilidades analíticas y de resolución de problemas. Excelentes habilidades de comunicación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Ingeniero Eléctrico en Terreno</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Transportes Depetris</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Camina, Región I</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Full-time - Presencial</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>https://www.laborum.cl/empleos/ingeniero-electrico-en-terreno-1118372791.html</t>
+        </is>
+      </c>
+      <c r="G423" t="n">
+        <v>0</v>
+      </c>
+      <c r="H423" t="inlineStr"/>
+      <c r="I423" t="n">
+        <v>0</v>
+      </c>
+      <c r="J423" t="n">
+        <v>0</v>
+      </c>
+      <c r="K423" t="n">
+        <v>0</v>
+      </c>
+      <c r="L423" t="n">
+        <v>1</v>
+      </c>
+      <c r="M423" t="n">
+        <v>0</v>
+      </c>
+      <c r="N423" t="n">
+        <v>0</v>
+      </c>
+      <c r="O423" t="n">
+        <v>0</v>
+      </c>
+      <c r="P423" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>Ingeniero Eléctrico en Terreno Resumen del Puesto Estamos en la búsqueda de un Ingeniero Eléctrico en Terreno con experiencia para unirse a nuestro equipo. El candidato ideal poseerá un sólido conocimiento técnico en sistemas eléctricos y la capacidad de gestionar proyectos en entornos de campo, asegurando la calidad y eficiencia en cada intervención. Responsabilidades  Supervisar y ejecutar instalaciones y mantenimientos de sistemas eléctricos en diversas ubicaciones. Realizar diagnósticos y solucionar problemas técnicos en equipos e instalaciones. Garantizar el cumplimiento de normativas y estándares de seguridad eléctrica. Coordinar con equipos de trabajo y proveedores para la correcta ejecución de las tareas. Elaborar informes técnicos y de avance de los proyectos.  Requisitos  Título universitario en Ingeniería Eléctrica o carrera afín. Experiencia comprobable en trabajos de terreno relacionados con sistemas eléctricos. Conocimiento en normativas y seguridad eléctrica. Habilidades para la resolución de problemas y toma de decisiones en campo. Capacidad para trabajar de forma autónoma y en equipo. Disponibilidad para desplazamientos según requerimientos del proyecto.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
